--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.833333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="G2" t="n">
-        <v>5.833333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.833333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>8.75</v>
       </c>
       <c r="G5" t="n">
-        <v>12.08333333333333</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -671,37 +671,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>15.08333333333333</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="F7" t="n">
-        <v>7.916666666666667</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -710,37 +710,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>12.77777777777778</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>11.11111111111111</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>23.88888888888889</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>38</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -803,16 +803,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>6.666666666666667</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>29.66666666666667</v>
+        <v>25.41666666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -878,16 +878,16 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>33.66666666666667</v>
+        <v>25.41666666666666</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>38.66666666666667</v>
+        <v>30.41666666666666</v>
       </c>
       <c r="H12" t="n">
         <v>43</v>
@@ -905,40 +905,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>32.11111111111111</v>
+        <v>25.5</v>
       </c>
       <c r="F13" t="n">
-        <v>12.22222222222222</v>
+        <v>9.5</v>
       </c>
       <c r="G13" t="n">
-        <v>44.33333333333334</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I13" t="n">
-        <v>26.33333333333334</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>158</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -949,110 +949,110 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>12.5</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>50.5</v>
+        <v>45.83333333333333</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>38.66666666666667</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="F15" t="n">
-        <v>4.583333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>43.25000000000001</v>
+        <v>42.77777777777778</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>4.777777777777779</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>62.11111111111112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>43.25000000000001</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>8.75</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>52.00000000000001</v>
+        <v>41</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,37 +1061,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>44.33333333333334</v>
+        <v>41</v>
       </c>
       <c r="F17" t="n">
-        <v>13.33333333333333</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>57.66666666666667</v>
+        <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,37 +1100,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>50.5</v>
+        <v>43.77777777777778</v>
       </c>
       <c r="F18" t="n">
-        <v>7.5</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>57.11111111111111</v>
       </c>
       <c r="H18" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1148,67 +1148,67 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>55.00000000000001</v>
+        <v>46.83333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>6.666666666666667</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G19" t="n">
-        <v>61.66666666666667</v>
+        <v>55.99999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>37.99999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>227.9999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>57.66666666666667</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>9.444444444444445</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>67.11111111111111</v>
+        <v>59</v>
       </c>
       <c r="H20" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,76 +1217,76 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>63.99999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>6.25</v>
       </c>
       <c r="G21" t="n">
-        <v>69</v>
+        <v>70.25</v>
       </c>
       <c r="H21" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>61.66666666666667</v>
+        <v>57.11111111111111</v>
       </c>
       <c r="F22" t="n">
-        <v>8.333333333333334</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>66.55555555555556</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,51 +1295,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>67.11111111111111</v>
+        <v>63</v>
       </c>
       <c r="F23" t="n">
-        <v>11.66666666666667</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
-        <v>78.77777777777779</v>
+        <v>74.5</v>
       </c>
       <c r="H23" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7777777777777857</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>7.777777777777857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1349,31 +1349,31 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>66.55555555555556</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>76</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="H24" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.2222222222222285</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.222222222222285</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1382,28 +1382,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>70.25</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>75</v>
+        <v>79.41666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1412,76 +1412,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>74.5</v>
       </c>
       <c r="F26" t="n">
-        <v>9.583333333333334</v>
+        <v>6.5</v>
       </c>
       <c r="G26" t="n">
-        <v>88.58333333333333</v>
+        <v>81</v>
       </c>
       <c r="H26" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I26" t="n">
-        <v>6.583333333333329</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>39.49999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>78.22222222222223</v>
       </c>
       <c r="F27" t="n">
-        <v>6.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G27" t="n">
-        <v>84.5</v>
+        <v>88.77777777777779</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,40 +1490,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>78.77777777777779</v>
+        <v>79.41666666666667</v>
       </c>
       <c r="F28" t="n">
-        <v>10.55555555555556</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>89.33333333333334</v>
+        <v>85.25</v>
       </c>
       <c r="H28" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J28" t="n">
         <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>96.5</v>
+        <v>93</v>
       </c>
       <c r="H29" t="n">
         <v>104</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.25</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>6.25</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77777777777778</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>12.77777777777778</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6.25</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
         <v>8.75</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -650,28 +650,28 @@
         <v>8.5</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,25 +683,25 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>12.77777777777778</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>11.11111111111111</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G7" t="n">
-        <v>23.88888888888889</v>
+        <v>21.77777777777778</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -710,7 +710,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -722,28 +722,28 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>5.833333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="G8" t="n">
-        <v>20.83333333333333</v>
+        <v>22.41666666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.416666666666668</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>54.16666666666668</v>
       </c>
     </row>
     <row r="9">
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
         <v>31</v>
@@ -788,76 +788,76 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>20.83333333333333</v>
+        <v>26.77777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>4.583333333333333</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G10" t="n">
-        <v>25.41666666666666</v>
+        <v>37.88888888888889</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>9.888888888888886</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>118.6666666666666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23.88888888888889</v>
+        <v>22.41666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>7.222222222222222</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>31.11111111111111</v>
+        <v>32</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,85 +866,85 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>25.41666666666666</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="G12" t="n">
-        <v>30.41666666666666</v>
+        <v>48.5</v>
       </c>
       <c r="H12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>25.5</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H13" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,25 +956,25 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>35.41666666666666</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>10.41666666666667</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>45.83333333333333</v>
+        <v>41.58333333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -995,64 +995,64 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>31.11111111111111</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F15" t="n">
-        <v>11.66666666666667</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G15" t="n">
-        <v>42.77777777777778</v>
+        <v>48.33333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="I15" t="n">
-        <v>4.777777777777779</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>62.11111111111112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>41.58333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>8.75</v>
       </c>
       <c r="G16" t="n">
-        <v>41</v>
+        <v>50.33333333333334</v>
       </c>
       <c r="H16" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1066,23 +1066,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>52.33333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>61.22222222222221</v>
       </c>
       <c r="H17" t="n">
         <v>63</v>
@@ -1100,46 +1100,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>43.77777777777778</v>
+        <v>48.5</v>
       </c>
       <c r="F18" t="n">
-        <v>13.33333333333333</v>
+        <v>11.5</v>
       </c>
       <c r="G18" t="n">
-        <v>57.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="H18" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J18" t="n">
         <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1148,37 +1148,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>46.83333333333333</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>9.166666666666666</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>55.99999999999999</v>
+        <v>61.16666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I19" t="n">
-        <v>37.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>227.9999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H20" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1226,37 +1226,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>63.99999999999999</v>
+        <v>61.16666666666667</v>
       </c>
       <c r="F21" t="n">
         <v>6.25</v>
       </c>
       <c r="G21" t="n">
-        <v>70.25</v>
+        <v>67.41666666666667</v>
       </c>
       <c r="H21" t="n">
         <v>70</v>
       </c>
       <c r="I21" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>57.11111111111111</v>
+        <v>61.22222222222221</v>
       </c>
       <c r="F22" t="n">
-        <v>9.444444444444445</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G22" t="n">
-        <v>66.55555555555556</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,37 +1295,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>63</v>
+        <v>68.41666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5</v>
+        <v>8.75</v>
       </c>
       <c r="G23" t="n">
-        <v>74.5</v>
+        <v>77.16666666666667</v>
       </c>
       <c r="H23" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,118 +1334,118 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>66.55555555555556</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
-        <v>11.66666666666667</v>
+        <v>6.5</v>
       </c>
       <c r="G24" t="n">
-        <v>78.22222222222223</v>
+        <v>79.5</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2222222222222285</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>2.222222222222285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>70.25</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>9.166666666666666</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>79.41666666666667</v>
+        <v>79</v>
       </c>
       <c r="H25" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>87.16666666666667</v>
+      </c>
+      <c r="H26" t="n">
+        <v>66</v>
+      </c>
+      <c r="I26" t="n">
+        <v>21.16666666666667</v>
+      </c>
+      <c r="J26" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>81</v>
-      </c>
-      <c r="H26" t="n">
-        <v>86</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>190.5000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1463,16 +1463,16 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>78.22222222222223</v>
+        <v>87</v>
       </c>
       <c r="F27" t="n">
         <v>10.55555555555556</v>
       </c>
       <c r="G27" t="n">
-        <v>88.77777777777779</v>
+        <v>97.55555555555556</v>
       </c>
       <c r="H27" t="n">
         <v>113</v>
@@ -1490,79 +1490,79 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>79.41666666666667</v>
+        <v>82.5</v>
       </c>
       <c r="F28" t="n">
-        <v>5.833333333333333</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>85.25</v>
+        <v>91.5</v>
       </c>
       <c r="H28" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="I28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>84</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>93</v>
+        <v>96.33333333333334</v>
       </c>
       <c r="H29" t="n">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>78.33333333333334</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>470.0000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.416666666666667</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>5.416666666666667</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.416666666666667</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>8.75</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>14.16666666666667</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="F6" t="n">
-        <v>9.5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>18.88888888888889</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,40 +671,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>13.41666666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>7.777777777777778</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>21.77777777777778</v>
+        <v>20.5</v>
       </c>
       <c r="H7" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -715,71 +715,71 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>16.16666666666667</v>
+        <v>13.5</v>
       </c>
       <c r="F8" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="G8" t="n">
-        <v>22.41666666666667</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
         <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>5.416666666666668</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>54.16666666666668</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>20.88888888888889</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>27.55555555555556</v>
       </c>
       <c r="H9" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,124 +788,124 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>26.77777777777778</v>
+        <v>24.5</v>
       </c>
       <c r="F10" t="n">
-        <v>11.11111111111111</v>
+        <v>8.75</v>
       </c>
       <c r="G10" t="n">
-        <v>37.88888888888889</v>
+        <v>33.25</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I10" t="n">
-        <v>9.888888888888886</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>118.6666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>22.41666666666667</v>
+        <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>9.583333333333334</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H11" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>30.55555555555556</v>
       </c>
       <c r="F12" t="n">
-        <v>12.5</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G12" t="n">
-        <v>48.5</v>
+        <v>39.44444444444444</v>
       </c>
       <c r="H12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>8.444444444444443</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>92.88888888888887</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,25 +917,25 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>38.25</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>37</v>
+        <v>44.08333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,31 +944,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
-        <v>4.583333333333333</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>41.58333333333334</v>
+        <v>47</v>
       </c>
       <c r="H14" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -992,37 +992,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>38.88888888888889</v>
+        <v>39.44444444444444</v>
       </c>
       <c r="F15" t="n">
-        <v>9.444444444444445</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>48.33333333333333</v>
+        <v>49.44444444444444</v>
       </c>
       <c r="H15" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>35.44444444444444</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>283.5555555555555</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1031,115 +1031,115 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>41.58333333333334</v>
+        <v>44.08333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>8.75</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>50.33333333333334</v>
+        <v>54.5</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J16" t="n">
         <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>52.33333333333333</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
-        <v>8.888888888888889</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>61.22222222222221</v>
+        <v>59</v>
       </c>
       <c r="H17" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>48.5</v>
+        <v>49.44444444444444</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G18" t="n">
         <v>60</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>360</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>55.33333333333334</v>
+        <v>54.5</v>
       </c>
       <c r="F19" t="n">
-        <v>5.833333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="G19" t="n">
-        <v>61.16666666666667</v>
+        <v>60.75</v>
       </c>
       <c r="H19" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1190,64 +1190,64 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>71</v>
       </c>
       <c r="H20" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>61.16666666666667</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>6.25</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G21" t="n">
-        <v>67.41666666666667</v>
+        <v>71.11111111111111</v>
       </c>
       <c r="H21" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,67 +1256,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>61.22222222222221</v>
+        <v>61.75</v>
       </c>
       <c r="F22" t="n">
-        <v>11.11111111111111</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>72.33333333333333</v>
+        <v>71.75</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>68.41666666666667</v>
+        <v>71</v>
       </c>
       <c r="F23" t="n">
-        <v>8.75</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>77.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="H23" t="n">
         <v>78</v>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,157 +1334,157 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>75.11111111111111</v>
       </c>
       <c r="F24" t="n">
-        <v>6.5</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G24" t="n">
-        <v>79.5</v>
+        <v>87.88888888888889</v>
       </c>
       <c r="H24" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5.888888888888886</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>35.33333333333331</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>72.33333333333333</v>
+        <v>71.75</v>
       </c>
       <c r="F25" t="n">
-        <v>6.666666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G25" t="n">
-        <v>79</v>
+        <v>80.5</v>
       </c>
       <c r="H25" t="n">
         <v>78</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>77.16666666666667</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>86</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="G26" t="n">
-        <v>87.16666666666667</v>
-      </c>
-      <c r="H26" t="n">
-        <v>66</v>
-      </c>
-      <c r="I26" t="n">
-        <v>21.16666666666667</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
       <c r="K26" t="n">
-        <v>190.5000000000001</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>80.5</v>
       </c>
       <c r="F27" t="n">
-        <v>10.55555555555556</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>97.55555555555556</v>
+        <v>87.58333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>18.58333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>130.0833333333333</v>
       </c>
     </row>
     <row r="28">
@@ -1499,19 +1499,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>82.5</v>
+        <v>90.5</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>91.5</v>
+        <v>99.5</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1529,7 +1529,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1538,31 +1538,31 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>87.58333333333333</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="G29" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>113</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>12</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>87.16666666666667</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9.166666666666666</v>
-      </c>
-      <c r="G29" t="n">
-        <v>96.33333333333334</v>
-      </c>
-      <c r="H29" t="n">
-        <v>18</v>
-      </c>
-      <c r="I29" t="n">
-        <v>78.33333333333334</v>
-      </c>
-      <c r="J29" t="n">
-        <v>6</v>
-      </c>
       <c r="K29" t="n">
-        <v>470.0000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.583333333333333</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>4.583333333333333</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.222222222222222</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>7.222222222222222</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,28 +605,28 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>4.583333333333333</v>
+        <v>11.58333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>5.833333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="G5" t="n">
-        <v>10.41666666666667</v>
+        <v>17.83333333333334</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.8333333333333357</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.333333333333357</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,13 +647,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7.222222222222222</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>11.66666666666667</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>18.88888888888889</v>
+        <v>20.5</v>
       </c>
       <c r="H6" t="n">
         <v>38</v>
@@ -676,74 +676,74 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>13.41666666666667</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.083333333333333</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G7" t="n">
-        <v>20.5</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="H7" t="n">
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>4.444444444444443</v>
       </c>
       <c r="J7" t="n">
         <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>88</v>
+        <v>71.11111111111109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>13.5</v>
+        <v>17.83333333333334</v>
       </c>
       <c r="F8" t="n">
-        <v>7.5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -761,16 +761,16 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>20.88888888888889</v>
+        <v>23.44444444444444</v>
       </c>
       <c r="F9" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>27.55555555555556</v>
+        <v>30.11111111111111</v>
       </c>
       <c r="H9" t="n">
         <v>43</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="F10" t="n">
-        <v>8.75</v>
+        <v>5.5</v>
       </c>
       <c r="G10" t="n">
-        <v>33.25</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,40 +827,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="G11" t="n">
-        <v>36</v>
+        <v>32.41666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -871,7 +871,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -881,100 +881,100 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>30.55555555555556</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>8.888888888888889</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>39.44444444444444</v>
+        <v>39</v>
       </c>
       <c r="H12" t="n">
         <v>31</v>
       </c>
       <c r="I12" t="n">
-        <v>8.444444444444443</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>92.88888888888887</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>38.25</v>
+        <v>35.11111111111111</v>
       </c>
       <c r="F13" t="n">
-        <v>5.833333333333333</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>44.08333333333334</v>
+        <v>42.33333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>6.333333333333336</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>57.00000000000002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>37.41666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -983,12 +983,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -998,114 +998,114 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>39.44444444444444</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G15" t="n">
-        <v>49.44444444444444</v>
+        <v>48.5</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I15" t="n">
-        <v>35.44444444444444</v>
+        <v>16.5</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>283.5555555555555</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>44.08333333333334</v>
+        <v>42.33333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>10.41666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>54.5</v>
+        <v>50.66666666666667</v>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="I16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>53.66666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="I17" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1115,61 +1115,61 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>49.44444444444444</v>
+        <v>48.5</v>
       </c>
       <c r="F18" t="n">
-        <v>10.55555555555556</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="H18" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="I18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51.66666666666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="G19" t="n">
+        <v>61.11111111111111</v>
+      </c>
+      <c r="H19" t="n">
+        <v>69</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="H19" t="n">
-        <v>70</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>12</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,51 +1178,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>54.66666666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>71</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>54.5</v>
       </c>
       <c r="F21" t="n">
-        <v>11.11111111111111</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>71.11111111111111</v>
+        <v>62.5</v>
       </c>
       <c r="H21" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,46 +1256,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
         <v>8</v>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
       <c r="E22" t="n">
-        <v>61.75</v>
+        <v>69.11111111111111</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G22" t="n">
-        <v>71.75</v>
+        <v>81.33333333333334</v>
       </c>
       <c r="H22" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>5.75</v>
+        <v>0.3333333333333428</v>
       </c>
       <c r="J22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>51.75</v>
+        <v>3.666666666666771</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1304,28 +1304,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>62.5</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>77</v>
+        <v>72.5</v>
       </c>
       <c r="H23" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,193 +1334,193 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>75.11111111111111</v>
+        <v>64.66666666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>12.77777777777778</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G24" t="n">
-        <v>87.88888888888889</v>
+        <v>73.83333333333334</v>
       </c>
       <c r="H24" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
-        <v>5.888888888888886</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>35.33333333333331</v>
+        <v>335.0000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>71.75</v>
+        <v>76.5</v>
       </c>
       <c r="F25" t="n">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="G25" t="n">
-        <v>80.5</v>
+        <v>83</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>81</v>
+        <v>73.83333333333334</v>
       </c>
       <c r="F26" t="n">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="G26" t="n">
-        <v>87.5</v>
+        <v>82.58333333333334</v>
       </c>
       <c r="H26" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>4.583333333333343</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>15</v>
+        <v>45.83333333333343</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" t="n">
+        <v>92.33333333333334</v>
+      </c>
+      <c r="F27" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="F27" t="n">
-        <v>7.083333333333333</v>
-      </c>
       <c r="G27" t="n">
-        <v>87.58333333333333</v>
+        <v>102.3333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="I27" t="n">
-        <v>18.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>130.0833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>90.5</v>
+        <v>82.58333333333334</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G28" t="n">
-        <v>99.5</v>
+        <v>90.50000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,40 +1529,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>87.58333333333333</v>
+        <v>83</v>
       </c>
       <c r="F29" t="n">
-        <v>7.916666666666667</v>
+        <v>11.5</v>
       </c>
       <c r="G29" t="n">
-        <v>95.5</v>
+        <v>94.5</v>
       </c>
       <c r="H29" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.583333333333334</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>9.583333333333334</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" t="n">
-        <v>28</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="H4" t="n">
+        <v>35</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,51 +593,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>11.58333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>17.83333333333334</v>
+        <v>19.5</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8333333333333357</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>8.333333333333357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G6" t="n">
-        <v>20.5</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="H6" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,36 +686,36 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>9.444444444444445</v>
+        <v>8.75</v>
       </c>
       <c r="G7" t="n">
-        <v>19.44444444444444</v>
+        <v>17.08333333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I7" t="n">
-        <v>4.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>71.11111111111109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>17.83333333333334</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="F8" t="n">
-        <v>5.833333333333333</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>23.66666666666667</v>
+        <v>20.55555555555556</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,37 +749,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>23.44444444444444</v>
+        <v>17.08333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>6.666666666666667</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>30.11111111111111</v>
+        <v>22.5</v>
       </c>
       <c r="H9" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -800,151 +800,151 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>23.66666666666667</v>
+        <v>23.55555555555556</v>
       </c>
       <c r="F11" t="n">
-        <v>8.75</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G11" t="n">
-        <v>32.41666666666667</v>
+        <v>33</v>
       </c>
       <c r="H11" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>39</v>
+        <v>32.91666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>35.11111111111111</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>7.222222222222222</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>42.33333333333334</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="I13" t="n">
-        <v>6.333333333333336</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>57.00000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,19 +956,19 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>37.41666666666667</v>
+        <v>34.91666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>10.41666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G14" t="n">
-        <v>47.83333333333334</v>
+        <v>43.66666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -983,12 +983,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -998,31 +998,31 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>9.5</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G15" t="n">
-        <v>48.5</v>
+        <v>41.88888888888889</v>
       </c>
       <c r="H15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" t="n">
-        <v>16.5</v>
+        <v>10.88888888888889</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>115.5</v>
+        <v>119.7777777777777</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>42.33333333333334</v>
+        <v>41.88888888888889</v>
       </c>
       <c r="F16" t="n">
-        <v>8.333333333333334</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G16" t="n">
-        <v>50.66666666666667</v>
+        <v>52.44444444444444</v>
       </c>
       <c r="H16" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>20.44444444444444</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>143.1111111111111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1076,22 +1076,22 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>47.83333333333334</v>
+        <v>43.66666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>5.833333333333333</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>53.66666666666667</v>
+        <v>49.08333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1109,67 +1109,67 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>54.5</v>
+        <v>57</v>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J18" t="n">
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>51.66666666666667</v>
+        <v>54.08333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>9.444444444444445</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G19" t="n">
-        <v>61.11111111111111</v>
+        <v>63.25</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,40 +1178,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>54.66666666666667</v>
+        <v>60.44444444444444</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G20" t="n">
-        <v>64.66666666666667</v>
+        <v>69.88888888888889</v>
       </c>
       <c r="H20" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.8888888888888857</v>
       </c>
       <c r="J20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>6.2222222222222</v>
       </c>
     </row>
     <row r="21">
@@ -1226,70 +1226,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>54.5</v>
+        <v>57</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="H21" t="n">
         <v>63</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>69.11111111111111</v>
+        <v>63.25</v>
       </c>
       <c r="F22" t="n">
-        <v>12.22222222222222</v>
+        <v>6.25</v>
       </c>
       <c r="G22" t="n">
-        <v>81.33333333333334</v>
+        <v>69.5</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3333333333333428</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>3.666666666666771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1304,37 +1304,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>62.5</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H23" t="n">
         <v>74</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,184 +1343,184 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>64.66666666666667</v>
+        <v>70.5</v>
       </c>
       <c r="F24" t="n">
-        <v>9.166666666666666</v>
+        <v>8.75</v>
       </c>
       <c r="G24" t="n">
-        <v>73.83333333333334</v>
+        <v>79.25</v>
       </c>
       <c r="H24" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>55.83333333333334</v>
+        <v>1.25</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>335.0000000000001</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>76.5</v>
+        <v>69.88888888888889</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G25" t="n">
-        <v>83</v>
+        <v>82.11111111111111</v>
       </c>
       <c r="H25" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>64.11111111111111</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>384.6666666666667</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>73.83333333333334</v>
+        <v>75</v>
       </c>
       <c r="F26" t="n">
-        <v>8.75</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>82.58333333333334</v>
+        <v>81</v>
       </c>
       <c r="H26" t="n">
         <v>78</v>
       </c>
       <c r="I26" t="n">
-        <v>4.583333333333343</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>45.83333333333343</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>92.33333333333334</v>
+        <v>84.25</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G27" t="n">
-        <v>102.3333333333333</v>
+        <v>93.83333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>70.99999999999997</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>82.58333333333334</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>7.916666666666667</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>90.50000000000001</v>
+        <v>90</v>
       </c>
       <c r="H28" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,40 +1529,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>83</v>
+        <v>82.11111111111111</v>
       </c>
       <c r="F29" t="n">
-        <v>11.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>94.5</v>
+        <v>92.66666666666667</v>
       </c>
       <c r="H29" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="I29" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8.333333333333334</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="n">
-        <v>8.333333333333334</v>
+        <v>7.5</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.777777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>7.777777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,37 +593,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>19.5</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="F6" t="n">
         <v>7.777777777777778</v>
       </c>
-      <c r="F6" t="n">
-        <v>6.111111111111111</v>
-      </c>
       <c r="G6" t="n">
-        <v>13.88888888888889</v>
+        <v>16.11111111111111</v>
       </c>
       <c r="H6" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,51 +671,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>8.333333333333334</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>17.08333333333334</v>
+        <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>13.88888888888889</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="F8" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>20.55555555555556</v>
+        <v>21.25</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -754,23 +754,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>17.08333333333334</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="F9" t="n">
-        <v>5.416666666666667</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G9" t="n">
-        <v>22.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="H9" t="n">
         <v>36</v>
@@ -788,90 +788,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19.5</v>
+        <v>21.25</v>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G10" t="n">
+        <v>27.91666666666667</v>
+      </c>
+      <c r="H10" t="n">
         <v>31</v>
       </c>
-      <c r="H10" t="n">
-        <v>20</v>
-      </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>11</v>
       </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
       <c r="K10" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23.55555555555556</v>
+        <v>27.91666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>9.444444444444445</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>33</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>3.833333333333336</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>288</v>
+        <v>26.83333333333335</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -881,31 +881,31 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>10.41666666666667</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>32.91666666666667</v>
+        <v>41.11111111111111</v>
       </c>
       <c r="H12" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -914,37 +914,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
-        <v>44</v>
+        <v>39.5</v>
       </c>
       <c r="H13" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -953,76 +953,76 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39.83333333333334</v>
+      </c>
+      <c r="F14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>34.91666666666667</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8.75</v>
-      </c>
       <c r="G14" t="n">
-        <v>43.66666666666667</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.833333333333336</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>18.33333333333336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>39.5</v>
       </c>
       <c r="F15" t="n">
-        <v>8.888888888888889</v>
+        <v>12.5</v>
       </c>
       <c r="G15" t="n">
-        <v>41.88888888888889</v>
+        <v>52</v>
       </c>
       <c r="H15" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>10.88888888888889</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>119.7777777777777</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>41.88888888888889</v>
+        <v>43.11111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>10.55555555555556</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G16" t="n">
-        <v>52.44444444444444</v>
+        <v>49.22222222222223</v>
       </c>
       <c r="H16" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>20.44444444444444</v>
+        <v>0.2222222222222285</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>143.1111111111111</v>
+        <v>2.444444444444514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1070,106 +1070,106 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>43.66666666666667</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>5.416666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G17" t="n">
-        <v>49.08333333333334</v>
+        <v>53.58333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.5833333333333357</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>8.1666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
         <v>5</v>
       </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>54.22222222222223</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>57</v>
+        <v>62.55555555555556</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="I18" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>69</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>7</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>54.08333333333334</v>
-      </c>
-      <c r="F19" t="n">
-        <v>9.166666666666666</v>
-      </c>
-      <c r="G19" t="n">
-        <v>63.25</v>
-      </c>
-      <c r="H19" t="n">
-        <v>81</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>11</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,46 +1178,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>60.44444444444444</v>
+        <v>53.58333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>9.444444444444445</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>69.88888888888889</v>
+        <v>63.16666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8888888888888857</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1232,61 +1232,61 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>61.5</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>73.5</v>
       </c>
       <c r="H21" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>16</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>63.25</v>
+        <v>62.55555555555556</v>
       </c>
       <c r="F22" t="n">
-        <v>6.25</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G22" t="n">
-        <v>69.5</v>
+        <v>74.77777777777779</v>
       </c>
       <c r="H22" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1300,35 +1300,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>66.16666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="H23" t="n">
         <v>74</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
@@ -1339,85 +1339,85 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>70.5</v>
+        <v>73.5</v>
       </c>
       <c r="F24" t="n">
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>79.25</v>
+        <v>84</v>
       </c>
       <c r="H24" t="n">
         <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>78</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>69.88888888888889</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12.22222222222222</v>
-      </c>
-      <c r="G25" t="n">
-        <v>82.11111111111111</v>
-      </c>
-      <c r="H25" t="n">
-        <v>18</v>
-      </c>
-      <c r="I25" t="n">
-        <v>64.11111111111111</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6</v>
-      </c>
       <c r="K25" t="n">
-        <v>384.6666666666667</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1427,31 +1427,31 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>75</v>
+        <v>74.77777777777779</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G26" t="n">
-        <v>81</v>
+        <v>82.55555555555556</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1460,31 +1460,31 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="G27" t="n">
+        <v>88.91666666666667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.916666666666671</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
       </c>
-      <c r="D27" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>84.25</v>
-      </c>
-      <c r="F27" t="n">
-        <v>9.583333333333334</v>
-      </c>
-      <c r="G27" t="n">
-        <v>93.83333333333333</v>
-      </c>
-      <c r="H27" t="n">
-        <v>82</v>
-      </c>
-      <c r="I27" t="n">
-        <v>11.83333333333333</v>
-      </c>
-      <c r="J27" t="n">
-        <v>6</v>
-      </c>
       <c r="K27" t="n">
-        <v>70.99999999999997</v>
+        <v>29.16666666666671</v>
       </c>
     </row>
     <row r="28">
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>81</v>
+        <v>93.55555555555556</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>90</v>
+        <v>103.5555555555556</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>82.11111111111111</v>
+        <v>84</v>
       </c>
       <c r="F29" t="n">
-        <v>10.55555555555556</v>
+        <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>92.66666666666667</v>
+        <v>93.5</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,13 +494,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.583333333333334</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>9.583333333333334</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -605,34 +605,34 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>11.58333333333333</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>17.83333333333334</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8333333333333357</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>8.333333333333357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,34 +683,34 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
+        <v>13.44444444444444</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21.77777777777778</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.777777777777779</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="F7" t="n">
-        <v>9.444444444444445</v>
-      </c>
-      <c r="G7" t="n">
-        <v>19.44444444444444</v>
-      </c>
-      <c r="H7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.444444444444443</v>
-      </c>
-      <c r="J7" t="n">
-        <v>16</v>
-      </c>
       <c r="K7" t="n">
-        <v>71.11111111111109</v>
+        <v>47.77777777777779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>17.83333333333334</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>5.833333333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>23.66666666666667</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,37 +749,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>23.44444444444444</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>6.666666666666667</v>
+        <v>9.5</v>
       </c>
       <c r="G9" t="n">
-        <v>30.11111111111111</v>
+        <v>26.5</v>
       </c>
       <c r="H9" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>22.5</v>
+        <v>21.77777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,22 +842,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23.66666666666667</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F11" t="n">
         <v>8.75</v>
       </c>
       <c r="G11" t="n">
-        <v>32.41666666666667</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -878,34 +878,34 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,28 +917,28 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>35.11111111111111</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="F13" t="n">
-        <v>7.222222222222222</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>42.33333333333334</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I13" t="n">
-        <v>6.333333333333336</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>57.00000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -956,16 +956,16 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>37.41666666666667</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F14" t="n">
         <v>10.41666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>47.83333333333334</v>
+        <v>42.5</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -995,34 +995,34 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>48.5</v>
+        <v>45</v>
       </c>
       <c r="H15" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="I15" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>115.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>42.33333333333334</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="F16" t="n">
-        <v>8.333333333333334</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>50.66666666666667</v>
+        <v>47.88888888888889</v>
       </c>
       <c r="H16" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1073,34 +1073,34 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>47.83333333333334</v>
+        <v>43.5</v>
       </c>
       <c r="F17" t="n">
-        <v>5.833333333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G17" t="n">
-        <v>53.66666666666667</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="H17" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1115,16 +1115,16 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>48.5</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1151,25 +1151,25 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>51.66666666666667</v>
+        <v>52.88888888888889</v>
       </c>
       <c r="F19" t="n">
-        <v>9.444444444444445</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>61.11111111111111</v>
+        <v>61.22222222222222</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1190,16 +1190,16 @@
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>54.66666666666667</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>64.66666666666667</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="H20" t="n">
         <v>66</v>
@@ -1217,7 +1217,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>62.5</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1268,39 +1268,39 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>69.11111111111111</v>
+        <v>61.22222222222222</v>
       </c>
       <c r="F22" t="n">
-        <v>12.22222222222222</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G22" t="n">
-        <v>81.33333333333334</v>
+        <v>69</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3333333333333428</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
-        <v>3.666666666666771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1310,103 +1310,103 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>62.5</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>72.5</v>
+        <v>69.75</v>
       </c>
       <c r="H23" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>64.66666666666667</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>9.166666666666666</v>
+        <v>11.5</v>
       </c>
       <c r="G24" t="n">
-        <v>73.83333333333334</v>
+        <v>78.5</v>
       </c>
       <c r="H24" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="I24" t="n">
-        <v>55.83333333333334</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>335.0000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>76.5</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G25" t="n">
-        <v>83</v>
+        <v>81.22222222222223</v>
       </c>
       <c r="H25" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.2222222222222285</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2.444444444444514</v>
       </c>
     </row>
     <row r="26">
@@ -1427,25 +1427,25 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>73.83333333333334</v>
+        <v>69.75</v>
       </c>
       <c r="F26" t="n">
         <v>8.75</v>
       </c>
       <c r="G26" t="n">
-        <v>82.58333333333334</v>
+        <v>78.5</v>
       </c>
       <c r="H26" t="n">
         <v>78</v>
       </c>
       <c r="I26" t="n">
-        <v>4.583333333333343</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>45.83333333333343</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1456,23 +1456,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>92.33333333333334</v>
+        <v>82.5</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G27" t="n">
-        <v>102.3333333333333</v>
+        <v>90</v>
       </c>
       <c r="H27" t="n">
         <v>104</v>
@@ -1490,37 +1490,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>85</v>
+      </c>
+      <c r="H28" t="n">
+        <v>86</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>82.58333333333334</v>
-      </c>
-      <c r="F28" t="n">
-        <v>7.916666666666667</v>
-      </c>
-      <c r="G28" t="n">
-        <v>90.50000000000001</v>
-      </c>
-      <c r="H28" t="n">
-        <v>113</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,40 +1529,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>83</v>
+        <v>82.22222222222223</v>
       </c>
       <c r="F29" t="n">
-        <v>11.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>94.5</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="H29" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="I29" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.333333333333334</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G4" t="n">
-        <v>8.333333333333334</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>7.083333333333333</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>14.58333333333333</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.333333333333334</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>7.777777777777778</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>16.11111111111111</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,46 +671,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>13.44444444444444</v>
       </c>
       <c r="F7" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21.77777777777778</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.777777777777779</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="G7" t="n">
-        <v>29</v>
-      </c>
-      <c r="H7" t="n">
-        <v>28</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>47.77777777777779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>14.58333333333333</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>6.666666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>21.25</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,37 +749,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>21.11111111111111</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>7.222222222222222</v>
+        <v>9.5</v>
       </c>
       <c r="G9" t="n">
-        <v>28.33333333333333</v>
+        <v>26.5</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>21.25</v>
+        <v>21.77777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>6.666666666666667</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G10" t="n">
-        <v>27.91666666666667</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,115 +836,115 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>27.91666666666667</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>7.916666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G11" t="n">
-        <v>35.83333333333334</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I11" t="n">
-        <v>3.833333333333336</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>26.83333333333335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>28.33333333333333</v>
+        <v>30.5</v>
       </c>
       <c r="F12" t="n">
-        <v>12.77777777777778</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>41.11111111111111</v>
+        <v>36</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I12" t="n">
-        <v>21.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>39.5</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="H13" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -953,37 +953,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>39.83333333333334</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>44.83333333333334</v>
+        <v>42.5</v>
       </c>
       <c r="H14" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>1.833333333333336</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>18.33333333333336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -992,37 +992,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1034,34 +1034,34 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>43.11111111111111</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="F16" t="n">
-        <v>6.111111111111111</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>49.22222222222223</v>
+        <v>47.88888888888889</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2222222222222285</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>2.444444444444514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1070,67 +1070,67 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>44.83333333333334</v>
+        <v>43.5</v>
       </c>
       <c r="F17" t="n">
-        <v>8.75</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G17" t="n">
-        <v>53.58333333333334</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5833333333333357</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>8.1666666666667</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>54.22222222222223</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>8.333333333333334</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>62.55555555555556</v>
+        <v>53</v>
       </c>
       <c r="H18" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
         <v>5</v>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>52.88888888888889</v>
       </c>
       <c r="F19" t="n">
-        <v>8.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>61.5</v>
+        <v>61.22222222222222</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>53.58333333333334</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="F20" t="n">
-        <v>9.583333333333334</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>63.16666666666667</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="H20" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1226,37 +1226,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>61.5</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>73.5</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I21" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>62.55555555555556</v>
+        <v>61.22222222222222</v>
       </c>
       <c r="F22" t="n">
-        <v>12.22222222222222</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G22" t="n">
-        <v>74.77777777777779</v>
+        <v>69</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1304,37 +1304,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>66.16666666666667</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="F23" t="n">
-        <v>8.333333333333334</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>74.5</v>
+        <v>69.75</v>
       </c>
       <c r="H23" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J23" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>7.5</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,115 +1343,115 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>73.5</v>
+        <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G24" t="n">
-        <v>84</v>
+        <v>78.5</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>6</v>
       </c>
-      <c r="J24" t="n">
-        <v>10</v>
-      </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>74.5</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G25" t="n">
-        <v>79.5</v>
+        <v>81.22222222222223</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.2222222222222285</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>12</v>
+        <v>2.444444444444514</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>74.77777777777779</v>
+        <v>69.75</v>
       </c>
       <c r="F26" t="n">
-        <v>7.777777777777778</v>
+        <v>8.75</v>
       </c>
       <c r="G26" t="n">
-        <v>82.55555555555556</v>
+        <v>78.5</v>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1460,67 +1460,67 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="F27" t="n">
-        <v>5.416666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="G27" t="n">
-        <v>88.91666666666667</v>
+        <v>90</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I27" t="n">
-        <v>2.916666666666671</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>29.16666666666671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>93.55555555555556</v>
+        <v>78.5</v>
       </c>
       <c r="F28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>85</v>
+      </c>
+      <c r="H28" t="n">
+        <v>86</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>10</v>
-      </c>
-      <c r="G28" t="n">
-        <v>103.5555555555556</v>
-      </c>
-      <c r="H28" t="n">
-        <v>104</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>9</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>84</v>
+        <v>82.22222222222223</v>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>93.5</v>
+        <v>92.77777777777779</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.416666666666667</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>5.416666666666667</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9.444444444444445</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G4" t="n">
-        <v>9.444444444444445</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.416666666666667</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>9.583333333333334</v>
+        <v>6.25</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>12.08333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -647,64 +647,64 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F6" t="n">
         <v>9</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" t="n">
-        <v>31</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>11</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>13.44444444444444</v>
+        <v>15.08333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>8.333333333333334</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>21.77777777777778</v>
+        <v>23</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I7" t="n">
-        <v>4.777777777777779</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>47.77777777777779</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -715,23 +715,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="F8" t="n">
-        <v>8.333333333333334</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G8" t="n">
-        <v>23.33333333333334</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="H8" t="n">
         <v>28</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>27.5</v>
       </c>
       <c r="F9" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="G9" t="n">
-        <v>26.5</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>21.77777777777778</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>7.777777777777778</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>29.55555555555556</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,37 +827,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23.33333333333334</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="F11" t="n">
-        <v>8.75</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G11" t="n">
-        <v>32.08333333333334</v>
+        <v>31.11111111111111</v>
       </c>
       <c r="H11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,37 +866,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>30.5</v>
+        <v>33.66666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>36</v>
+        <v>38.66666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,28 +917,28 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>29.55555555555556</v>
+        <v>32.11111111111111</v>
       </c>
       <c r="F13" t="n">
-        <v>6.666666666666667</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>36.22222222222222</v>
+        <v>44.33333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>26.33333333333334</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -949,71 +949,71 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>32.08333333333334</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>10.41666666666667</v>
+        <v>12.5</v>
       </c>
       <c r="G14" t="n">
-        <v>42.5</v>
+        <v>50.5</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>38.66666666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>43.25000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1027,23 +1027,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>36.22222222222222</v>
+        <v>43.25000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>11.66666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G16" t="n">
-        <v>47.88888888888889</v>
+        <v>52.00000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>53</v>
@@ -1061,46 +1061,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>43.5</v>
+        <v>44.33333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>9.166666666666666</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>52.66666666666666</v>
+        <v>57.66666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I17" t="n">
-        <v>34.66666666666666</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>50.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H18" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>52.88888888888889</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>61.22222222222222</v>
+        <v>61.66666666666667</v>
       </c>
       <c r="H19" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>57.66666666666667</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="G20" t="n">
+        <v>67.11111111111111</v>
+      </c>
+      <c r="H20" t="n">
+        <v>69</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>52.66666666666666</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>62.66666666666666</v>
-      </c>
-      <c r="H20" t="n">
-        <v>66</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>9</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H21" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,37 +1256,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>61.22222222222222</v>
+        <v>61.66666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>7.777777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,46 +1295,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>62.66666666666666</v>
+        <v>67.11111111111111</v>
       </c>
       <c r="F23" t="n">
-        <v>7.083333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>69.75</v>
+        <v>78.77777777777779</v>
       </c>
       <c r="H23" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I23" t="n">
-        <v>0.75</v>
+        <v>0.7777777777777857</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>5.25</v>
+        <v>7.777777777777857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,28 +1343,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>78.5</v>
+        <v>76</v>
       </c>
       <c r="H24" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,46 +1373,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>70</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>78</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>69</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12.22222222222222</v>
-      </c>
-      <c r="G25" t="n">
-        <v>81.22222222222223</v>
-      </c>
-      <c r="H25" t="n">
-        <v>81</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.2222222222222285</v>
-      </c>
-      <c r="J25" t="n">
-        <v>11</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.444444444444514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,67 +1421,67 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>69.75</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
-        <v>8.75</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G26" t="n">
-        <v>78.5</v>
+        <v>88.58333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>6.583333333333329</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>39.49999999999997</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>78</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="F27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>90</v>
-      </c>
-      <c r="H27" t="n">
-        <v>104</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>9</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,37 +1490,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>78.5</v>
+        <v>78.77777777777779</v>
       </c>
       <c r="F28" t="n">
-        <v>6.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G28" t="n">
-        <v>85</v>
+        <v>89.33333333333334</v>
       </c>
       <c r="H28" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,37 +1529,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>82.22222222222223</v>
+        <v>87.5</v>
       </c>
       <c r="F29" t="n">
-        <v>10.55555555555556</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>92.77777777777779</v>
+        <v>96.5</v>
       </c>
       <c r="H29" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.833333333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>5.833333333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G4" t="n">
-        <v>12.77777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.833333333333333</v>
+        <v>7.5</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>12.08333333333333</v>
+        <v>14.5</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,100 +647,100 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F6" t="n">
+        <v>9.583333333333334</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17.91666666666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>9</v>
       </c>
-      <c r="G6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>14</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>15.08333333333333</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="F7" t="n">
-        <v>7.916666666666667</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.444444444444443</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>43.55555555555554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>12.77777777777778</v>
+        <v>19.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.11111111111111</v>
+        <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>23.88888888888889</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,40 +749,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>27.5</v>
+        <v>18.91666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>10.5</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>38</v>
+        <v>28.08333333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>10.08333333333334</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>60.50000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -793,23 +793,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="F10" t="n">
-        <v>6.666666666666667</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G10" t="n">
-        <v>29.66666666666667</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="H10" t="n">
         <v>31</v>
@@ -827,37 +827,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23.88888888888889</v>
+        <v>28.08333333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>7.222222222222222</v>
+        <v>8.75</v>
       </c>
       <c r="G11" t="n">
-        <v>31.11111111111111</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,79 +866,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>33.66666666666667</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G12" t="n">
-        <v>38.66666666666667</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="H12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>6.888888888888886</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>48.2222222222222</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>32.11111111111111</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>12.22222222222222</v>
+        <v>6.5</v>
       </c>
       <c r="G13" t="n">
-        <v>44.33333333333334</v>
+        <v>36.5</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I13" t="n">
-        <v>26.33333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>158</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="14">
@@ -953,37 +953,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="F14" t="n">
         <v>12.5</v>
       </c>
       <c r="G14" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -992,67 +992,67 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>38.66666666666667</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>4.583333333333333</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>43.25000000000001</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3.833333333333336</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>38.33333333333336</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>43.25000000000001</v>
+        <v>42.88888888888889</v>
       </c>
       <c r="F16" t="n">
-        <v>8.75</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G16" t="n">
-        <v>52.00000000000001</v>
+        <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,46 +1061,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>44.33333333333334</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>13.33333333333333</v>
+        <v>8.75</v>
       </c>
       <c r="G17" t="n">
-        <v>57.66666666666667</v>
+        <v>55.58333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.583333333333336</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>36.1666666666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H18" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>55.00000000000001</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>6.666666666666667</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G19" t="n">
-        <v>61.66666666666667</v>
+        <v>61.77777777777778</v>
       </c>
       <c r="H19" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,241 +1178,241 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>57.66666666666667</v>
+        <v>58.58333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>9.444444444444445</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>67.11111111111111</v>
+        <v>65.25</v>
       </c>
       <c r="H20" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>61.77777777777778</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>69</v>
+        <v>70.11111111111111</v>
       </c>
       <c r="H21" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.1111111111111143</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.333333333333371</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>61.66666666666667</v>
+        <v>62</v>
       </c>
       <c r="F22" t="n">
-        <v>8.333333333333334</v>
+        <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>67.11111111111111</v>
+        <v>65.25</v>
       </c>
       <c r="F23" t="n">
-        <v>11.66666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>78.77777777777779</v>
+        <v>73.58333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7777777777777857</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>7.777777777777857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>70.11111111111111</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G24" t="n">
-        <v>76</v>
+        <v>82.33333333333334</v>
       </c>
       <c r="H24" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.333333333333343</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>14.66666666666677</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>70</v>
+        <v>75.5</v>
       </c>
       <c r="F25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>87</v>
+      </c>
+      <c r="H25" t="n">
+        <v>82</v>
+      </c>
+      <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="G25" t="n">
-        <v>75</v>
-      </c>
-      <c r="H25" t="n">
-        <v>78</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,31 +1421,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>73.58333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>9.583333333333334</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>88.58333333333333</v>
+        <v>78.58333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
-        <v>6.583333333333329</v>
+        <v>0.5833333333333286</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>39.49999999999997</v>
+        <v>4.666666666666629</v>
       </c>
     </row>
     <row r="27">
@@ -1456,41 +1456,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>78</v>
+        <v>82.58333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>6.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>84.5</v>
+        <v>88</v>
       </c>
       <c r="H27" t="n">
         <v>86</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1499,28 +1499,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>78.77777777777779</v>
+        <v>93.33333333333334</v>
       </c>
       <c r="F28" t="n">
-        <v>10.55555555555556</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>89.33333333333334</v>
+        <v>103.3333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1541,25 +1541,25 @@
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>87.5</v>
+        <v>93</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>96.5</v>
+        <v>102.5</v>
       </c>
       <c r="H29" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -611,19 +611,19 @@
         <v>7.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,7 +710,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -722,25 +722,25 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,64 +761,64 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>18.91666666666667</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>9.166666666666666</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>28.08333333333334</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I9" t="n">
-        <v>10.08333333333334</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>60.50000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19.44444444444444</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>8.888888888888889</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>28.33333333333333</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,37 +827,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>28.08333333333334</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="F11" t="n">
-        <v>8.75</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G11" t="n">
-        <v>36.83333333333334</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,12 +866,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -881,31 +881,31 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>28.33333333333333</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>10.55555555555556</v>
+        <v>8.75</v>
       </c>
       <c r="G12" t="n">
-        <v>38.88888888888889</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I12" t="n">
-        <v>6.888888888888886</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>48.2222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -914,76 +914,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
         <v>36.5</v>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>36.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>12.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>6.888888888888886</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>48.2222222222222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -995,64 +995,64 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>41.83333333333334</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>46.83333333333334</v>
+        <v>42.5</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>3.833333333333336</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>38.33333333333336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
       <c r="E16" t="n">
-        <v>42.88888888888889</v>
+        <v>41.5</v>
       </c>
       <c r="F16" t="n">
-        <v>6.111111111111111</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="n">
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,51 +1061,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>46.83333333333334</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F17" t="n">
-        <v>8.75</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G17" t="n">
-        <v>55.58333333333334</v>
+        <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I17" t="n">
-        <v>2.583333333333336</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>36.1666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1115,61 +1115,61 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G18" t="n">
-        <v>62</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="H18" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>7.777777777777778</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>61.77777777777778</v>
+        <v>62</v>
       </c>
       <c r="H19" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1183,46 +1183,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>58.58333333333334</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>6.666666666666667</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G20" t="n">
-        <v>65.25</v>
+        <v>58.88888888888889</v>
       </c>
       <c r="H20" t="n">
         <v>63</v>
       </c>
       <c r="I20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1232,36 +1232,36 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>61.77777777777778</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>8.333333333333334</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>70.11111111111111</v>
+        <v>59.75</v>
       </c>
       <c r="H21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1111111111111143</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>1.333333333333371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1271,31 +1271,31 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>62</v>
+        <v>58.88888888888889</v>
       </c>
       <c r="F22" t="n">
-        <v>8.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>70.5</v>
+        <v>65.55555555555556</v>
       </c>
       <c r="H22" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1307,25 +1307,25 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>65.25</v>
+        <v>67.75</v>
       </c>
       <c r="F23" t="n">
-        <v>8.333333333333334</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G23" t="n">
-        <v>73.58333333333333</v>
+        <v>76.91666666666667</v>
       </c>
       <c r="H23" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,12 +1334,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1349,25 +1349,25 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>70.11111111111111</v>
+        <v>62</v>
       </c>
       <c r="F24" t="n">
-        <v>12.22222222222222</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>82.33333333333334</v>
+        <v>72.5</v>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>1.333333333333343</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>14.66666666666677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1378,80 +1378,80 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>75.5</v>
+        <v>69.55555555555556</v>
       </c>
       <c r="F25" t="n">
-        <v>11.5</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G25" t="n">
-        <v>87</v>
+        <v>82.33333333333334</v>
       </c>
       <c r="H25" t="n">
         <v>82</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0.3333333333333428</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>2.000000000000057</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>73.58333333333333</v>
+        <v>77.5</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G26" t="n">
-        <v>78.58333333333333</v>
+        <v>84</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5833333333333286</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>4.666666666666629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1460,31 +1460,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>82.58333333333333</v>
+        <v>76.91666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>5.416666666666667</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>82.75</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1502,16 +1502,16 @@
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>93.33333333333334</v>
+        <v>85.33333333333334</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>103.3333333333333</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>93</v>
+        <v>83.75</v>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>102.5</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8.333333333333334</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="n">
-        <v>8.333333333333334</v>
+        <v>7.5</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9.444444444444445</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G4" t="n">
-        <v>9.444444444444445</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>13</v>
-      </c>
-      <c r="H5" t="n">
-        <v>49</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.333333333333334</v>
+        <v>7.5</v>
       </c>
       <c r="F6" t="n">
-        <v>9.583333333333334</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>17.91666666666667</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,100 +686,100 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9.444444444444445</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G7" t="n">
-        <v>19.44444444444444</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
-        <v>5.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>43.55555555555554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>18.58333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7.833333333333332</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>78.33333333333331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>17.91666666666667</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>5.416666666666667</v>
+        <v>5.5</v>
       </c>
       <c r="G9" t="n">
-        <v>23.33333333333334</v>
+        <v>24.5</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>31.66666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -832,41 +832,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
-        <v>19.44444444444444</v>
+        <v>27.5</v>
       </c>
       <c r="F11" t="n">
-        <v>8.888888888888889</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>28.33333333333333</v>
+        <v>35.5</v>
       </c>
       <c r="H11" t="n">
         <v>31</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>23.33333333333334</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>8.75</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>32.08333333333334</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,12 +905,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -920,22 +920,22 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>36.5</v>
+        <v>36.08333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -959,36 +959,36 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>28.33333333333333</v>
+        <v>31.66666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>10.55555555555556</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="G14" t="n">
-        <v>38.88888888888889</v>
+        <v>45.55555555555556</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>6.888888888888886</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>48.2222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -998,61 +998,61 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>32.08333333333334</v>
+        <v>35.5</v>
       </c>
       <c r="F15" t="n">
-        <v>10.41666666666667</v>
+        <v>9.5</v>
       </c>
       <c r="G15" t="n">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.08333333333333</v>
+      </c>
+      <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="E16" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>7.5</v>
-      </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>41.08333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,37 +1061,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>38.88888888888889</v>
+        <v>41.08333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>11.11111111111111</v>
+        <v>8.75</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>49.83333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,115 +1100,115 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>43.5</v>
+        <v>45</v>
       </c>
       <c r="F18" t="n">
-        <v>9.166666666666666</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>52.66666666666666</v>
+        <v>53</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="I18" t="n">
-        <v>34.66666666666666</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>46.55555555555556</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G19" t="n">
-        <v>62</v>
+        <v>58.77777777777778</v>
       </c>
       <c r="H19" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>40.77777777777778</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>244.6666666666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>54.83333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>8.888888888888889</v>
+        <v>6.25</v>
       </c>
       <c r="G20" t="n">
-        <v>58.88888888888889</v>
+        <v>61.08333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,12 +1217,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>52.66666666666666</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>7.083333333333333</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>59.75</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1265,28 +1265,28 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>58.77777777777778</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="G22" t="n">
+        <v>68.22222222222223</v>
+      </c>
+      <c r="H22" t="n">
+        <v>69</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>58.88888888888889</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="G22" t="n">
-        <v>65.55555555555556</v>
-      </c>
-      <c r="H22" t="n">
-        <v>78</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>8</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1304,19 +1304,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>67.75</v>
+        <v>61.08333333333333</v>
       </c>
       <c r="F23" t="n">
         <v>9.166666666666666</v>
       </c>
       <c r="G23" t="n">
-        <v>76.91666666666667</v>
+        <v>70.25</v>
       </c>
       <c r="H23" t="n">
         <v>81</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1349,22 +1349,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>72.5</v>
+        <v>72</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1382,81 +1382,81 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>69.55555555555556</v>
+        <v>68.22222222222223</v>
       </c>
       <c r="F25" t="n">
-        <v>12.77777777777778</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>82.33333333333334</v>
+        <v>79.8888888888889</v>
       </c>
       <c r="H25" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3333333333333428</v>
+        <v>1.8888888888889</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>2.000000000000057</v>
+        <v>18.888888888889</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>66</v>
+      </c>
+      <c r="I26" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="J26" t="n">
         <v>9</v>
       </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>84</v>
-      </c>
-      <c r="H26" t="n">
-        <v>86</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>137.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1466,22 +1466,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>76.91666666666667</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>82.75</v>
+        <v>78</v>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,40 +1490,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>85.33333333333334</v>
+        <v>82</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="G28" t="n">
-        <v>95.33333333333334</v>
+        <v>93.5</v>
       </c>
       <c r="H28" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>83.75</v>
+        <v>79.8888888888889</v>
       </c>
       <c r="F29" t="n">
-        <v>7.916666666666667</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>91.66666666666667</v>
+        <v>90.44444444444446</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G4" t="n">
-        <v>12.77777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F5" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,7 +632,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>7.083333333333333</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>14.58333333333333</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,7 +671,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -686,100 +686,100 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>12.77777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="F7" t="n">
-        <v>11.11111111111111</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>23.88888888888889</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.444444444444443</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>43.55555555555554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>18.58333333333333</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>24.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I8" t="n">
-        <v>7.833333333333332</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>78.33333333333331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>24.5</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>23.88888888888889</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>7.777777777777778</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>31.66666666666667</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -832,41 +832,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>27.5</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G11" t="n">
-        <v>35.5</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="H11" t="n">
         <v>31</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>49.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>24.83333333333333</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F12" t="n">
-        <v>5.833333333333333</v>
+        <v>8.75</v>
       </c>
       <c r="G12" t="n">
-        <v>30.66666666666666</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,12 +905,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -920,22 +920,22 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>30.66666666666666</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>5.416666666666667</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
-        <v>36.08333333333333</v>
+        <v>36.5</v>
       </c>
       <c r="H13" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -959,36 +959,36 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>31.66666666666667</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>13.88888888888889</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G14" t="n">
-        <v>45.55555555555556</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>6.888888888888886</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>48.2222222222222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -998,61 +998,61 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>35.5</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>9.5</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="H15" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>36.08333333333333</v>
+        <v>41.5</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="n">
-        <v>41.08333333333333</v>
+        <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,37 +1061,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>41.08333333333333</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F17" t="n">
-        <v>8.75</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G17" t="n">
-        <v>49.83333333333333</v>
+        <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,115 +1100,115 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G18" t="n">
-        <v>53</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="H18" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>46.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>12.22222222222222</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>58.77777777777778</v>
+        <v>62</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I19" t="n">
-        <v>40.77777777777778</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>244.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8.888888888888889</v>
+      </c>
+      <c r="G20" t="n">
+        <v>58.88888888888889</v>
+      </c>
+      <c r="H20" t="n">
+        <v>63</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>54.83333333333333</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="G20" t="n">
-        <v>61.08333333333333</v>
-      </c>
-      <c r="H20" t="n">
-        <v>70</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,12 +1217,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>63</v>
+        <v>59.75</v>
       </c>
       <c r="H21" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1265,28 +1265,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>58.77777777777778</v>
+        <v>58.88888888888889</v>
       </c>
       <c r="F22" t="n">
-        <v>9.444444444444445</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>68.22222222222223</v>
+        <v>65.55555555555556</v>
       </c>
       <c r="H22" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1304,19 +1304,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>61.08333333333333</v>
+        <v>67.75</v>
       </c>
       <c r="F23" t="n">
         <v>9.166666666666666</v>
       </c>
       <c r="G23" t="n">
-        <v>70.25</v>
+        <v>76.91666666666667</v>
       </c>
       <c r="H23" t="n">
         <v>81</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1349,22 +1349,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="H24" t="n">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1382,81 +1382,81 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>68.22222222222223</v>
+        <v>69.55555555555556</v>
       </c>
       <c r="F25" t="n">
-        <v>11.66666666666667</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G25" t="n">
-        <v>79.8888888888889</v>
+        <v>82.33333333333334</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8888888888889</v>
+        <v>0.3333333333333428</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>18.888888888889</v>
+        <v>2.000000000000057</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>84</v>
+      </c>
+      <c r="H26" t="n">
+        <v>86</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="F26" t="n">
-        <v>10</v>
-      </c>
-      <c r="G26" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="H26" t="n">
-        <v>66</v>
-      </c>
-      <c r="I26" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
       <c r="K26" t="n">
-        <v>137.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1466,22 +1466,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>76.91666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>78</v>
+        <v>82.75</v>
       </c>
       <c r="H27" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,40 +1490,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>85.33333333333334</v>
+      </c>
+      <c r="F28" t="n">
         <v>10</v>
       </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="n">
-        <v>82</v>
-      </c>
-      <c r="F28" t="n">
-        <v>11.5</v>
-      </c>
       <c r="G28" t="n">
-        <v>93.5</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="H28" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I28" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>79.8888888888889</v>
+        <v>83.75</v>
       </c>
       <c r="F29" t="n">
-        <v>10.55555555555556</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>90.44444444444446</v>
+        <v>91.66666666666667</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8.333333333333334</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>8.333333333333334</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
         <v>7.5</v>
       </c>
-      <c r="F5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,36 +647,36 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.333333333333334</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="F6" t="n">
-        <v>9.583333333333334</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>17.91666666666667</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>5.444444444444443</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>43.55555555555554</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,31 +686,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9.444444444444445</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>19.44444444444444</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
-        <v>5.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>43.55555555555554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -767,19 +767,19 @@
         <v>17.91666666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>5.416666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G9" t="n">
-        <v>23.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="F10" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="n">
+        <v>32</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>26</v>
-      </c>
-      <c r="H10" t="n">
-        <v>35</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -832,23 +832,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
-        <v>19.44444444444444</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>8.888888888888889</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>28.33333333333333</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
         <v>31</v>
@@ -866,7 +866,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>23.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>8.75</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G12" t="n">
         <v>32.08333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,37 +905,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G13" t="n">
-        <v>36.5</v>
+        <v>41.11111111111111</v>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,40 +944,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" t="n">
-        <v>28.33333333333333</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>10.55555555555556</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>38.88888888888889</v>
+        <v>41</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I14" t="n">
-        <v>6.888888888888886</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>48.2222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1022,7 +1022,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1034,25 +1034,25 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>51.5</v>
       </c>
       <c r="H16" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1076,22 +1076,22 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>38.88888888888889</v>
+        <v>41.11111111111111</v>
       </c>
       <c r="F17" t="n">
-        <v>11.11111111111111</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
       </c>
       <c r="H17" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>62</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="H19" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>56.5</v>
       </c>
       <c r="F20" t="n">
-        <v>8.888888888888889</v>
+        <v>7.5</v>
       </c>
       <c r="G20" t="n">
-        <v>58.88888888888889</v>
+        <v>64</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1235,19 +1235,19 @@
         <v>52.66666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>7.083333333333333</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>59.75</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="H21" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1268,25 +1268,25 @@
         <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>58.88888888888889</v>
+        <v>60.66666666666666</v>
       </c>
       <c r="F22" t="n">
-        <v>6.666666666666667</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G22" t="n">
-        <v>65.55555555555556</v>
+        <v>67.88888888888889</v>
       </c>
       <c r="H22" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1307,34 +1307,34 @@
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>67.75</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="F23" t="n">
-        <v>9.166666666666666</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>76.91666666666667</v>
+        <v>69.75</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1349,22 +1349,22 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1385,67 +1385,67 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>69.55555555555556</v>
+        <v>67.88888888888889</v>
       </c>
       <c r="F25" t="n">
         <v>12.77777777777778</v>
       </c>
       <c r="G25" t="n">
-        <v>82.33333333333334</v>
+        <v>80.66666666666666</v>
       </c>
       <c r="H25" t="n">
         <v>82</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3333333333333428</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.000000000000057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>77.5</v>
+        <v>69.75</v>
       </c>
       <c r="F26" t="n">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="G26" t="n">
-        <v>84</v>
+        <v>78.5</v>
       </c>
       <c r="H26" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1466,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>76.91666666666667</v>
+        <v>75</v>
       </c>
       <c r="F27" t="n">
-        <v>5.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>82.75</v>
+        <v>82</v>
       </c>
       <c r="H27" t="n">
         <v>85</v>
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>85.33333333333334</v>
+        <v>82.5</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G28" t="n">
-        <v>95.33333333333334</v>
+        <v>90</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>83.75</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="F29" t="n">
-        <v>7.916666666666667</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>91.66666666666667</v>
+        <v>97.22222222222221</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9.444444444444445</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>9.444444444444445</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -608,13 +608,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>7.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
         <v>17</v>
@@ -632,51 +632,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>9.444444444444445</v>
+        <v>10.58333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G6" t="n">
-        <v>19.44444444444444</v>
+        <v>19.75</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>5.444444444444443</v>
+        <v>1.75</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>43.55555555555554</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,31 +686,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9.583333333333334</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.333333333333334</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G7" t="n">
-        <v>17.91666666666667</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="H7" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4.444444444444443</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>71.11111111111109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -722,64 +722,64 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="F8" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>28.5</v>
       </c>
       <c r="H8" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>17.91666666666667</v>
+        <v>23.44444444444444</v>
       </c>
       <c r="F9" t="n">
-        <v>8.75</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G9" t="n">
-        <v>26.66666666666667</v>
+        <v>31.22222222222222</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,12 +788,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -803,22 +803,22 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19.44444444444444</v>
+        <v>19.75</v>
       </c>
       <c r="F10" t="n">
-        <v>10.55555555555556</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -839,34 +839,34 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>28.5</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -878,34 +878,34 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>26.66666666666667</v>
+        <v>33.75</v>
       </c>
       <c r="F12" t="n">
-        <v>5.416666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>32.08333333333334</v>
+        <v>40.41666666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>9.416666666666664</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>103.5833333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,22 +920,22 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>31.22222222222222</v>
       </c>
       <c r="F13" t="n">
-        <v>11.11111111111111</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>41.11111111111111</v>
+        <v>42.88888888888889</v>
       </c>
       <c r="H13" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,34 +956,34 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="G14" t="n">
-        <v>41</v>
+        <v>51.5</v>
       </c>
       <c r="H14" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -998,94 +998,94 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>32.08333333333334</v>
+        <v>40.41666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>10.41666666666667</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>42.5</v>
+        <v>48.33333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>114.3333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>41</v>
+        <v>47.88888888888889</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G16" t="n">
-        <v>51.5</v>
+        <v>55.11111111111111</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>19.11111111111111</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>48.33333333333333</v>
+      </c>
+      <c r="F17" t="n">
         <v>5</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>41.11111111111111</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8.888888888888889</v>
-      </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>53.33333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1100,70 +1100,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>43.5</v>
+        <v>53.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9.166666666666666</v>
+        <v>5.5</v>
       </c>
       <c r="G18" t="n">
-        <v>52.66666666666666</v>
+        <v>59</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
-        <v>34.66666666666666</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>208</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>53.33333333333333</v>
       </c>
       <c r="F19" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="G19" t="n">
-        <v>56.66666666666666</v>
+        <v>59.99999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>56.5</v>
+        <v>55.11111111111111</v>
       </c>
       <c r="F20" t="n">
-        <v>7.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>64</v>
+        <v>63.44444444444444</v>
       </c>
       <c r="H20" t="n">
         <v>70</v>
@@ -1217,12 +1217,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1232,22 +1232,22 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>52.66666666666666</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>86</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>62.66666666666666</v>
-      </c>
-      <c r="H21" t="n">
-        <v>66</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>9</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,37 +1256,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>60.66666666666666</v>
+        <v>59.99999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>7.222222222222222</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G22" t="n">
-        <v>67.88888888888889</v>
+        <v>68.33333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,46 +1295,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>62.66666666666666</v>
+        <v>63.44444444444444</v>
       </c>
       <c r="F23" t="n">
-        <v>7.083333333333333</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G23" t="n">
-        <v>69.75</v>
+        <v>75.66666666666666</v>
       </c>
       <c r="H23" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="I23" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1346,28 +1346,28 @@
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>64</v>
+        <v>71.5</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1378,23 +1378,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>67.88888888888889</v>
+        <v>72.33333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>12.77777777777778</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>80.66666666666666</v>
+        <v>81.91666666666666</v>
       </c>
       <c r="H25" t="n">
         <v>82</v>
@@ -1412,76 +1412,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>69.75</v>
+        <v>75.66666666666666</v>
       </c>
       <c r="F26" t="n">
-        <v>8.75</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G26" t="n">
-        <v>78.5</v>
+        <v>83.44444444444443</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>84.91666666666666</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>92.41666666666666</v>
+      </c>
+      <c r="H27" t="n">
+        <v>104</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>9</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>75</v>
-      </c>
-      <c r="F27" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" t="n">
-        <v>82</v>
-      </c>
-      <c r="H27" t="n">
-        <v>85</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,40 +1490,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="F28" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G28" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="H28" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="29">
@@ -1541,16 +1541,16 @@
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>86.66666666666666</v>
+        <v>84.44444444444443</v>
       </c>
       <c r="F29" t="n">
         <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>97.22222222222221</v>
+        <v>94.99999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,13 +494,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9.583333333333334</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>9.583333333333334</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,154 +632,154 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10.58333333333333</v>
+        <v>8.5</v>
       </c>
       <c r="F6" t="n">
-        <v>9.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>19.75</v>
+        <v>17.5</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>9.444444444444445</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>19.44444444444444</v>
+        <v>21.25</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>4.444444444444443</v>
+        <v>1.25</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>71.11111111111109</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>18.5</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="F8" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25.55555555555556</v>
+      </c>
+      <c r="H8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8.555555555555557</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="G8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>28</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>12</v>
-      </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>85.55555555555557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>23.44444444444444</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7.777777777777778</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>31.22222222222222</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -797,37 +797,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19.75</v>
+        <v>21.25</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>29.75</v>
+        <v>29.58333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.583333333333336</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19.00000000000003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,256 +842,256 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>33.75</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="F12" t="n">
-        <v>6.666666666666667</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>40.41666666666666</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12" t="n">
-        <v>9.416666666666664</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>103.5833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>31.22222222222222</v>
+        <v>29.58333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>11.66666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G13" t="n">
-        <v>42.88888888888889</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.3333333333333357</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4.333333333333364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>12.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>51.5</v>
+        <v>40</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>40.41666666666666</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>7.916666666666667</v>
+        <v>10.5</v>
       </c>
       <c r="G15" t="n">
-        <v>48.33333333333333</v>
+        <v>49.5</v>
       </c>
       <c r="H15" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I15" t="n">
-        <v>16.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>114.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>47.88888888888889</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>7.222222222222222</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>55.11111111111111</v>
+        <v>48.75</v>
       </c>
       <c r="H16" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>19.11111111111111</v>
+        <v>0.75</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>172</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>48.33333333333333</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G17" t="n">
-        <v>53.33333333333333</v>
+        <v>46.11111111111111</v>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,46 +1100,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>53.5</v>
+        <v>46.11111111111111</v>
       </c>
       <c r="F18" t="n">
-        <v>5.5</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G18" t="n">
-        <v>59</v>
+        <v>58.88888888888889</v>
       </c>
       <c r="H18" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1151,25 +1151,25 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>53.33333333333333</v>
+        <v>49.75</v>
       </c>
       <c r="F19" t="n">
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>59.99999999999999</v>
+        <v>59.75</v>
       </c>
       <c r="H19" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>55.11111111111111</v>
+        <v>52.5</v>
       </c>
       <c r="F20" t="n">
-        <v>8.333333333333334</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>63.44444444444444</v>
+        <v>60.5</v>
       </c>
       <c r="H20" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="F21" t="n">
-        <v>6.5</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G21" t="n">
-        <v>65.5</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="H21" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>59.99999999999999</v>
+        <v>59.75</v>
       </c>
       <c r="F22" t="n">
-        <v>8.333333333333334</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>68.33333333333333</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,12 +1295,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1310,22 +1310,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>63.44444444444444</v>
+        <v>60.5</v>
       </c>
       <c r="F23" t="n">
-        <v>12.22222222222222</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>75.66666666666666</v>
+        <v>70.5</v>
       </c>
       <c r="H23" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1339,71 +1339,71 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>71.5</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="G24" t="n">
-        <v>82</v>
+        <v>75.58333333333333</v>
       </c>
       <c r="H24" t="n">
         <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>72.33333333333333</v>
+        <v>70.5</v>
       </c>
       <c r="F25" t="n">
-        <v>9.583333333333334</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>81.91666666666666</v>
+        <v>76.5</v>
       </c>
       <c r="H25" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1412,37 +1412,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>75.66666666666666</v>
+        <v>80.58333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>7.777777777777778</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>83.44444444444443</v>
+        <v>86</v>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1451,37 +1451,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>84.91666666666666</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="F27" t="n">
-        <v>7.5</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G27" t="n">
-        <v>92.41666666666666</v>
+        <v>83.88888888888889</v>
       </c>
       <c r="H27" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1505,25 +1505,25 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>82</v>
+        <v>76.5</v>
       </c>
       <c r="F28" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>90.5</v>
+        <v>85.5</v>
       </c>
       <c r="H28" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="I28" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
-        <v>150.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1544,13 +1544,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>84.44444444444443</v>
+        <v>84.88888888888889</v>
       </c>
       <c r="F29" t="n">
         <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>94.99999999999999</v>
+        <v>95.44444444444444</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -611,19 +611,19 @@
         <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>11.66666666666667</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -671,79 +671,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>11.66666666666667</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="F7" t="n">
-        <v>9.583333333333334</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>21.25</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>1.25</v>
+        <v>8.555555555555557</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>11.25</v>
+        <v>85.55555555555557</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>17.22222222222222</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>8.333333333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>25.55555555555556</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
-        <v>8.555555555555557</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>85.55555555555557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -788,7 +788,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -803,25 +803,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>21.25</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>8.333333333333334</v>
+        <v>8.75</v>
       </c>
       <c r="G10" t="n">
-        <v>29.58333333333334</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I10" t="n">
-        <v>1.583333333333336</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>19.00000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -905,7 +905,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,25 +920,25 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>29.58333333333334</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>8.75</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>38.33333333333334</v>
+        <v>42.5</v>
       </c>
       <c r="H13" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3333333333333357</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>4.333333333333364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1001,19 +1001,19 @@
         <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
-        <v>49.5</v>
+        <v>44.5</v>
       </c>
       <c r="H15" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1022,76 +1022,76 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>38.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>10.41666666666667</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>48.75</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>43.5</v>
       </c>
       <c r="F17" t="n">
-        <v>6.111111111111111</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>46.11111111111111</v>
+        <v>53.5</v>
       </c>
       <c r="H17" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,12 +1100,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1115,22 +1115,22 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>46.11111111111111</v>
+        <v>44.5</v>
       </c>
       <c r="F18" t="n">
-        <v>12.77777777777778</v>
+        <v>6.5</v>
       </c>
       <c r="G18" t="n">
-        <v>58.88888888888889</v>
+        <v>51</v>
       </c>
       <c r="H18" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>49.75</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>59.75</v>
+        <v>62</v>
       </c>
       <c r="H19" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>52.5</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>60.5</v>
+        <v>65</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>63.88888888888889</v>
+        <v>53.5</v>
       </c>
       <c r="F21" t="n">
-        <v>12.22222222222222</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>76.11111111111111</v>
+        <v>60.58333333333334</v>
       </c>
       <c r="H21" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>59.75</v>
+        <v>60.58333333333334</v>
       </c>
       <c r="F22" t="n">
-        <v>7.083333333333333</v>
+        <v>8.75</v>
       </c>
       <c r="G22" t="n">
-        <v>66.83333333333333</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="H22" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1304,19 +1304,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>60.5</v>
+        <v>62</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>70.5</v>
+        <v>72</v>
       </c>
       <c r="H23" t="n">
         <v>74</v>
@@ -1334,37 +1334,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>66.83333333333333</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>8.75</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G24" t="n">
-        <v>75.58333333333333</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,76 +1373,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>70.5</v>
+        <v>74.33333333333334</v>
       </c>
       <c r="F25" t="n">
+        <v>9.583333333333334</v>
+      </c>
+      <c r="G25" t="n">
+        <v>83.91666666666667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>82</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.916666666666671</v>
+      </c>
+      <c r="J25" t="n">
         <v>6</v>
       </c>
-      <c r="G25" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>78</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>8</v>
-      </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>11.50000000000003</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>80.58333333333333</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>5.416666666666667</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>76.11111111111111</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="F27" t="n">
         <v>7.777777777777778</v>
       </c>
       <c r="G27" t="n">
-        <v>83.88888888888889</v>
+        <v>85</v>
       </c>
       <c r="H27" t="n">
         <v>85</v>
@@ -1499,19 +1499,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>76.5</v>
+        <v>78</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>85.5</v>
+        <v>87</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>84.88888888888889</v>
+        <v>89.91666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>10.55555555555556</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>95.44444444444444</v>
+        <v>97.83333333333334</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8.333333333333334</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>8.333333333333334</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>9.444444444444445</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G4" t="n">
-        <v>9.444444444444445</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,192 +647,192 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.333333333333334</v>
+        <v>8.5</v>
       </c>
       <c r="F6" t="n">
-        <v>9.583333333333334</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>17.91666666666667</v>
+        <v>17.5</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9.444444444444445</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>19.44444444444444</v>
+        <v>21.25</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>5.444444444444443</v>
+        <v>1.25</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>43.55555555555554</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>19.5</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>8.555555555555557</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>85.55555555555557</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>18.91666666666667</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="n">
-        <v>9.166666666666666</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>28.08333333333334</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I9" t="n">
-        <v>10.08333333333334</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>60.50000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>19.44444444444444</v>
+        <v>21.25</v>
       </c>
       <c r="F10" t="n">
-        <v>8.888888888888889</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>28.33333333333333</v>
+        <v>29.58333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.583333333333336</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19.00000000000003</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -842,31 +842,31 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>28.08333333333334</v>
+        <v>25.5</v>
       </c>
       <c r="F11" t="n">
-        <v>8.75</v>
+        <v>9.5</v>
       </c>
       <c r="G11" t="n">
-        <v>36.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="H11" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -875,262 +875,262 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>28.33333333333333</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="F12" t="n">
-        <v>10.55555555555556</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>38.88888888888889</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I12" t="n">
-        <v>6.888888888888886</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>48.2222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>29.58333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="G13" t="n">
-        <v>36.5</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333357</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.333333333333364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>36.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>12.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>41.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G15" t="n">
-        <v>46.83333333333334</v>
+        <v>49.5</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I15" t="n">
-        <v>3.833333333333336</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>38.33333333333336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>42.88888888888889</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>6.111111111111111</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>48.75</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>46.83333333333334</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>8.75</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G17" t="n">
-        <v>55.58333333333334</v>
+        <v>46.11111111111111</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I17" t="n">
-        <v>2.583333333333336</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
-        <v>36.1666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>46.11111111111111</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G18" t="n">
-        <v>62</v>
+        <v>58.88888888888889</v>
       </c>
       <c r="H18" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>49.75</v>
       </c>
       <c r="F19" t="n">
-        <v>7.777777777777778</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>61.77777777777778</v>
+        <v>59.75</v>
       </c>
       <c r="H19" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1183,41 +1183,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>58.58333333333334</v>
+        <v>52.5</v>
       </c>
       <c r="F20" t="n">
-        <v>6.666666666666667</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>65.25</v>
+        <v>60.5</v>
       </c>
       <c r="H20" t="n">
         <v>63</v>
       </c>
       <c r="I20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>8</v>
       </c>
       <c r="K20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1229,28 +1229,28 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>61.77777777777778</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="F21" t="n">
-        <v>8.333333333333334</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G21" t="n">
-        <v>70.11111111111111</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="H21" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1111111111111143</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>1.333333333333371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1261,35 +1261,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>62</v>
+        <v>59.75</v>
       </c>
       <c r="F22" t="n">
-        <v>8.5</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>70.5</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="H22" t="n">
         <v>69</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1300,23 +1300,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>65.25</v>
+        <v>60.5</v>
       </c>
       <c r="F23" t="n">
-        <v>8.333333333333334</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>73.58333333333333</v>
+        <v>70.5</v>
       </c>
       <c r="H23" t="n">
         <v>74</v>
@@ -1334,46 +1334,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>70.11111111111111</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>12.22222222222222</v>
+        <v>8.75</v>
       </c>
       <c r="G24" t="n">
-        <v>82.33333333333334</v>
+        <v>75.58333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
-        <v>1.333333333333343</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
-        <v>14.66666666666677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1385,34 +1385,34 @@
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>75.5</v>
+        <v>70.5</v>
       </c>
       <c r="F25" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>87</v>
+        <v>76.5</v>
       </c>
       <c r="H25" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,70 +1421,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>73.58333333333333</v>
+        <v>80.58333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>78.58333333333333</v>
+        <v>86</v>
       </c>
       <c r="H26" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5833333333333286</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>4.666666666666629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>82.58333333333333</v>
+        <v>76.11111111111111</v>
       </c>
       <c r="F27" t="n">
-        <v>5.416666666666667</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G27" t="n">
-        <v>88</v>
+        <v>83.88888888888889</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>93.33333333333334</v>
+        <v>76.5</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>103.3333333333333</v>
+        <v>85.5</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>93</v>
+        <v>84.88888888888889</v>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>102.5</v>
+        <v>95.44444444444444</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.416666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.416666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.22222222222222</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G4" t="n">
-        <v>12.22222222222222</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.416666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>11.66666666666667</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,139 +647,139 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>17.5</v>
+        <v>16.11111111111111</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>11.66666666666667</v>
+        <v>11.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9.583333333333334</v>
+        <v>6.5</v>
       </c>
       <c r="G7" t="n">
-        <v>21.25</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>17.22222222222222</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>8.333333333333334</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>25.55555555555556</v>
+        <v>22.5</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
-        <v>8.555555555555557</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>85.55555555555557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>17.5</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>32.77777777777778</v>
       </c>
       <c r="H9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -793,46 +793,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>21.25</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>8.333333333333334</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>29.58333333333334</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
         <v>28</v>
       </c>
       <c r="I10" t="n">
-        <v>1.583333333333336</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>19.00000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -842,70 +842,70 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>25.5</v>
+        <v>22.5</v>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>25.55555555555556</v>
+        <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>7.777777777777778</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>33.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,34 +917,34 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>29.58333333333334</v>
+        <v>33.16666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>8.75</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>38.33333333333334</v>
+        <v>37.75000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3333333333333357</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>4.333333333333364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -959,22 +959,22 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>33.33333333333334</v>
+        <v>32.77777777777778</v>
       </c>
       <c r="F14" t="n">
-        <v>6.666666666666667</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -983,37 +983,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37.75000000000001</v>
+      </c>
+      <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>39</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="G15" t="n">
-        <v>49.5</v>
+        <v>42.75000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1022,76 +1022,76 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>38.33333333333334</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>10.41666666666667</v>
+        <v>8.5</v>
       </c>
       <c r="G16" t="n">
-        <v>48.75</v>
+        <v>48.5</v>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="I16" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>42.75000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>6.111111111111111</v>
+        <v>8.75</v>
       </c>
       <c r="G17" t="n">
-        <v>46.11111111111111</v>
+        <v>51.50000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1109,28 +1109,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>46.11111111111111</v>
+        <v>46.66666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>12.77777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>58.88888888888889</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1144,23 +1144,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>49.75</v>
+        <v>48.5</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>59.75</v>
+        <v>60.5</v>
       </c>
       <c r="H19" t="n">
         <v>66</v>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>52.5</v>
+        <v>54.50000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>60.5</v>
+        <v>61.16666666666667</v>
       </c>
       <c r="H20" t="n">
         <v>63</v>
@@ -1226,19 +1226,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>63.88888888888889</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="F21" t="n">
         <v>12.22222222222222</v>
       </c>
       <c r="G21" t="n">
-        <v>76.11111111111111</v>
+        <v>67.22222222222223</v>
       </c>
       <c r="H21" t="n">
         <v>81</v>
@@ -1256,37 +1256,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>59.75</v>
+        <v>60.5</v>
       </c>
       <c r="F22" t="n">
-        <v>7.083333333333333</v>
+        <v>10.5</v>
       </c>
       <c r="G22" t="n">
-        <v>66.83333333333333</v>
+        <v>71</v>
       </c>
       <c r="H22" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1300,23 +1300,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>60.5</v>
+        <v>61.16666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>70.5</v>
+        <v>69.5</v>
       </c>
       <c r="H23" t="n">
         <v>74</v>
@@ -1334,37 +1334,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>66.83333333333333</v>
+        <v>69.22222222222223</v>
       </c>
       <c r="F24" t="n">
-        <v>8.75</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G24" t="n">
-        <v>75.58333333333333</v>
+        <v>82</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1378,23 +1378,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>70.5</v>
+        <v>69.5</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>76.5</v>
+        <v>74.5</v>
       </c>
       <c r="H25" t="n">
         <v>78</v>
@@ -1412,76 +1412,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>80.58333333333333</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
-        <v>5.416666666666667</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
         <v>86</v>
       </c>
       <c r="H26" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>76.11111111111111</v>
+        <v>78.5</v>
       </c>
       <c r="F27" t="n">
-        <v>7.777777777777778</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>83.88888888888889</v>
+        <v>83.91666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,37 +1490,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>76.5</v>
+        <v>88</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G28" t="n">
-        <v>85.5</v>
+        <v>98.55555555555556</v>
       </c>
       <c r="H28" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,37 +1529,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>86.91666666666667</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>94.41666666666667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>104</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>9</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>84.88888888888889</v>
-      </c>
-      <c r="F29" t="n">
-        <v>10.55555555555556</v>
-      </c>
-      <c r="G29" t="n">
-        <v>95.44444444444444</v>
-      </c>
-      <c r="H29" t="n">
-        <v>113</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>12</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,13 +533,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.777777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>7.777777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7.083333333333333</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14.58333333333333</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7.777777777777778</v>
+        <v>7.5</v>
       </c>
       <c r="F6" t="n">
-        <v>8.333333333333334</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>16.11111111111111</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,22 +686,22 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F7" t="n">
-        <v>6.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -710,7 +710,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -728,19 +728,19 @@
         <v>14.58333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>7.916666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>22.5</v>
+        <v>21.25</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>21.11111111111111</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>11.66666666666667</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G9" t="n">
-        <v>32.77777777777778</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,22 +842,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>22.5</v>
+        <v>21.25</v>
       </c>
       <c r="F11" t="n">
-        <v>6.666666666666667</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G11" t="n">
         <v>29.16666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -871,110 +871,110 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>28.77777777777778</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" t="n">
         <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>33.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>4.583333333333333</v>
+        <v>10.5</v>
       </c>
       <c r="G13" t="n">
-        <v>37.75000000000001</v>
+        <v>38.5</v>
       </c>
       <c r="H13" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>32.77777777777778</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>13.88888888888889</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>46.66666666666667</v>
+        <v>34.16666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -995,25 +995,25 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>37.75000000000001</v>
+        <v>38.16666666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G15" t="n">
         <v>42.75000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1037,61 +1037,61 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="F16" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="G16" t="n">
-        <v>48.5</v>
+        <v>51</v>
       </c>
       <c r="H16" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50.44444444444444</v>
+      </c>
+      <c r="H17" t="n">
+        <v>69</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>42.75000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="G17" t="n">
-        <v>51.50000000000001</v>
-      </c>
-      <c r="H17" t="n">
-        <v>53</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>14</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,37 +1100,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>46.66666666666667</v>
+        <v>42.75000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8.333333333333334</v>
+        <v>8.75</v>
       </c>
       <c r="G18" t="n">
-        <v>55.00000000000001</v>
+        <v>51.50000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1154,13 +1154,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>48.5</v>
+        <v>50.44444444444444</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>60.5</v>
+        <v>63.77777777777778</v>
       </c>
       <c r="H19" t="n">
         <v>66</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>54.50000000000001</v>
+        <v>51</v>
       </c>
       <c r="F20" t="n">
-        <v>6.666666666666667</v>
+        <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>61.16666666666667</v>
+        <v>58</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>55.00000000000001</v>
+        <v>54.50000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>12.22222222222222</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>67.22222222222223</v>
+        <v>61.16666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>60.5</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G22" t="n">
-        <v>71</v>
+        <v>65.5</v>
       </c>
       <c r="H22" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1346,25 +1346,25 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>69.22222222222223</v>
+        <v>63.77777777777778</v>
       </c>
       <c r="F24" t="n">
-        <v>12.77777777777778</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>82</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="H24" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,37 +1373,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>69.5</v>
+        <v>65.5</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>74.5</v>
+        <v>76.5</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1412,76 +1412,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>73.5</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G26" t="n">
-        <v>86</v>
+        <v>83.08333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.083333333333329</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>6.499999999999972</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>78.5</v>
+        <v>79.44444444444444</v>
       </c>
       <c r="F27" t="n">
-        <v>5.416666666666667</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>83.91666666666667</v>
+        <v>89.44444444444444</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,37 +1490,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>88</v>
+        <v>78.5</v>
       </c>
       <c r="F28" t="n">
-        <v>10.55555555555556</v>
+        <v>6.5</v>
       </c>
       <c r="G28" t="n">
-        <v>98.55555555555556</v>
+        <v>85</v>
       </c>
       <c r="H28" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1538,28 +1538,28 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>89.08333333333333</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="G29" t="n">
+        <v>97</v>
+      </c>
+      <c r="H29" t="n">
+        <v>113</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>12</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>86.91666666666667</v>
-      </c>
-      <c r="F29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>94.41666666666667</v>
-      </c>
-      <c r="H29" t="n">
-        <v>104</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>9</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,13 +533,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.333333333333334</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G4" t="n">
-        <v>8.333333333333334</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="F6" t="n">
-        <v>7.083333333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>14.58333333333333</v>
+        <v>16.11111111111111</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,22 +686,22 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8.333333333333334</v>
+        <v>11.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.666666666666667</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>21.5</v>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,64 +761,64 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>22.11111111111111</v>
       </c>
       <c r="F9" t="n">
-        <v>7.777777777777778</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G9" t="n">
-        <v>22.77777777777778</v>
+        <v>34.33333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>97.99999999999997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>21.25</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,37 +827,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>21.25</v>
+        <v>21.5</v>
       </c>
       <c r="F11" t="n">
-        <v>7.916666666666667</v>
+        <v>10.5</v>
       </c>
       <c r="G11" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,46 +866,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="D12" t="n">
-        <v>6</v>
-      </c>
       <c r="E12" t="n">
-        <v>28.77777777777778</v>
+        <v>33.16666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>12.22222222222222</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>41</v>
+        <v>38.16666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -920,61 +920,61 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="G13" t="n">
         <v>38.5</v>
       </c>
       <c r="H13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>6.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>29.16666666666667</v>
+        <v>34.33333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>34.16666666666667</v>
+        <v>47.66666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>38.16666666666667</v>
@@ -1061,37 +1061,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>41</v>
+        <v>42.75000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9.444444444444445</v>
+        <v>8.75</v>
       </c>
       <c r="G17" t="n">
-        <v>50.44444444444444</v>
+        <v>51.50000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,37 +1100,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>47.66666666666666</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.444444444444445</v>
+      </c>
+      <c r="G18" t="n">
+        <v>57.11111111111111</v>
+      </c>
+      <c r="H18" t="n">
+        <v>69</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>7</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>42.75000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="G18" t="n">
-        <v>51.50000000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>53</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,12 +1139,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1154,22 +1154,22 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>50.44444444444444</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>13.33333333333333</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="n">
-        <v>63.77777777777778</v>
+        <v>58.5</v>
       </c>
       <c r="H19" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>51</v>
+        <v>54.50000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>61.16666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>54.50000000000001</v>
+        <v>57.11111111111111</v>
       </c>
       <c r="F21" t="n">
-        <v>6.666666666666667</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>61.16666666666667</v>
+        <v>68.77777777777777</v>
       </c>
       <c r="H21" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>65.5</v>
+        <v>69.5</v>
       </c>
       <c r="H22" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1346,25 +1346,25 @@
         <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>63.77777777777778</v>
+        <v>76.77777777777777</v>
       </c>
       <c r="F24" t="n">
-        <v>11.66666666666667</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G24" t="n">
-        <v>75.44444444444444</v>
+        <v>84.55555555555554</v>
       </c>
       <c r="H24" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,37 +1373,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>78</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>11</v>
-      </c>
-      <c r="G25" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="H25" t="n">
-        <v>81</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>11</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1417,71 +1417,71 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>73.5</v>
+        <v>71.5</v>
       </c>
       <c r="F26" t="n">
-        <v>9.583333333333334</v>
+        <v>11.5</v>
       </c>
       <c r="G26" t="n">
-        <v>83.08333333333333</v>
+        <v>83</v>
       </c>
       <c r="H26" t="n">
         <v>82</v>
       </c>
       <c r="I26" t="n">
-        <v>1.083333333333329</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>6.499999999999972</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
         <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>79.44444444444444</v>
+        <v>78.5</v>
       </c>
       <c r="F27" t="n">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="G27" t="n">
+        <v>83.91666666666667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>86</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="G27" t="n">
-        <v>89.44444444444444</v>
-      </c>
-      <c r="H27" t="n">
-        <v>104</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>9</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1502,25 +1502,25 @@
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>78.5</v>
+        <v>86</v>
       </c>
       <c r="F28" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H28" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
         <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>89.08333333333333</v>
+        <v>89.91666666666667</v>
       </c>
       <c r="F29" t="n">
         <v>7.916666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>97</v>
+        <v>97.83333333333334</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,13 +533,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -593,12 +593,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,22 +608,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7.083333333333333</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14.58333333333333</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7.777777777777778</v>
+        <v>7.5</v>
       </c>
       <c r="F6" t="n">
-        <v>8.333333333333334</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>16.11111111111111</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -671,12 +671,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,22 +686,22 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="F7" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16.11111111111111</v>
+      </c>
+      <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>28</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -710,7 +710,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -728,19 +728,19 @@
         <v>14.58333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>6.666666666666667</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>21.25</v>
+        <v>22.5</v>
       </c>
       <c r="H8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -761,64 +761,64 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>22.11111111111111</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="F9" t="n">
-        <v>12.22222222222222</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>34.33333333333333</v>
+        <v>32.77777777777778</v>
       </c>
       <c r="H9" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I9" t="n">
-        <v>16.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>97.99999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>21.25</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>7.916666666666667</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>29.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,37 +827,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,37 +866,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>33.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G12" t="n">
-        <v>38.16666666666667</v>
+        <v>35.5</v>
       </c>
       <c r="H12" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,46 +905,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>33.16666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>38.5</v>
+        <v>37.75000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>22.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,64 +956,64 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>34.33333333333333</v>
+        <v>33.77777777777778</v>
       </c>
       <c r="F14" t="n">
-        <v>13.33333333333333</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G14" t="n">
-        <v>47.66666666666666</v>
+        <v>46</v>
       </c>
       <c r="H14" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>38.16666666666667</v>
+        <v>35.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4.583333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="G15" t="n">
-        <v>42.75000000000001</v>
+        <v>48</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1022,40 +1022,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>37.75000000000001</v>
+      </c>
+      <c r="F16" t="n">
         <v>5</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>12.5</v>
-      </c>
       <c r="G16" t="n">
-        <v>51</v>
+        <v>42.75000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1100,7 +1100,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1115,22 +1115,22 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>47.66666666666666</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>9.444444444444445</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>57.11111111111111</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1154,22 +1154,22 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>58.5</v>
+        <v>59</v>
       </c>
       <c r="H19" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>57.11111111111111</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>11.66666666666667</v>
+        <v>8.5</v>
       </c>
       <c r="G21" t="n">
-        <v>68.77777777777777</v>
+        <v>68.5</v>
       </c>
       <c r="H21" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,37 +1256,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>58.5</v>
+        <v>59.33333333333334</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>69.5</v>
+        <v>71</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>76.77777777777777</v>
+        <v>76.5</v>
       </c>
       <c r="F24" t="n">
-        <v>7.777777777777778</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>84.55555555555554</v>
+        <v>83.5</v>
       </c>
       <c r="H24" t="n">
         <v>85</v>
@@ -1412,46 +1412,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>71.5</v>
+        <v>76</v>
       </c>
       <c r="F26" t="n">
-        <v>11.5</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G26" t="n">
-        <v>83</v>
+        <v>83.22222222222223</v>
       </c>
       <c r="H26" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1469,22 +1469,22 @@
         <v>78.5</v>
       </c>
       <c r="F27" t="n">
-        <v>5.416666666666667</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G27" t="n">
-        <v>83.91666666666667</v>
+        <v>88.08333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>6.083333333333329</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>36.49999999999997</v>
       </c>
     </row>
     <row r="28">
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>86</v>
+        <v>86.22222222222223</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>95</v>
+        <v>96.22222222222223</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>89.91666666666667</v>
+        <v>84.5</v>
       </c>
       <c r="F29" t="n">
-        <v>7.916666666666667</v>
+        <v>9.5</v>
       </c>
       <c r="G29" t="n">
-        <v>97.83333333333334</v>
+        <v>94</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.777777777777778</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G4" t="n">
-        <v>7.777777777777778</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -608,13 +608,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
         <v>20</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,25 +647,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F6" t="n">
-        <v>7.083333333333333</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>14.58333333333333</v>
+        <v>17.5</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -683,34 +683,34 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>7.777777777777778</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="F7" t="n">
         <v>8.333333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>16.11111111111111</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="H7" t="n">
         <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>8.555555555555557</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>85.55555555555557</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>14.58333333333333</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>7.916666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>22.5</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,37 +749,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>21.11111111111111</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="n">
-        <v>11.66666666666667</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>32.77777777777778</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,37 +788,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>23.33333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="G10" t="n">
-        <v>28</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,12 +827,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -842,61 +842,61 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>22.5</v>
+        <v>25.5</v>
       </c>
       <c r="F11" t="n">
-        <v>6.666666666666667</v>
+        <v>9.5</v>
       </c>
       <c r="G11" t="n">
-        <v>29.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="H11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>25.55555555555556</v>
       </c>
       <c r="F12" t="n">
-        <v>7.5</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G12" t="n">
-        <v>35.5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="H12" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -917,25 +917,25 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>33.16666666666667</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>4.583333333333333</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>37.75000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="H13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,34 +956,34 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>33.77777777777778</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>12.22222222222222</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -995,25 +995,25 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>35.5</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>44.5</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1022,37 +1022,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>37.75000000000001</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>42.75000000000001</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1070,28 +1070,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>42.75000000000001</v>
+        <v>43.5</v>
       </c>
       <c r="F17" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>51.50000000000001</v>
+        <v>53.5</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,37 +1100,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="F18" t="n">
-        <v>13.33333333333333</v>
+        <v>6.5</v>
       </c>
       <c r="G18" t="n">
-        <v>59.33333333333334</v>
+        <v>51</v>
       </c>
       <c r="H18" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1148,28 +1148,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H19" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>54.50000000000001</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="F20" t="n">
-        <v>6.666666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>61.16666666666667</v>
+        <v>65</v>
       </c>
       <c r="H20" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>60</v>
+        <v>53.5</v>
       </c>
       <c r="F21" t="n">
-        <v>8.5</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>68.5</v>
+        <v>60.58333333333334</v>
       </c>
       <c r="H21" t="n">
         <v>69</v>
@@ -1261,23 +1261,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>59.33333333333334</v>
+        <v>60.58333333333334</v>
       </c>
       <c r="F22" t="n">
-        <v>11.66666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G22" t="n">
-        <v>71</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="H22" t="n">
         <v>78</v>
@@ -1300,23 +1300,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>61.16666666666667</v>
+        <v>62</v>
       </c>
       <c r="F23" t="n">
-        <v>8.333333333333334</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>69.5</v>
+        <v>72</v>
       </c>
       <c r="H23" t="n">
         <v>74</v>
@@ -1334,37 +1334,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>76.5</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G24" t="n">
-        <v>83.5</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="H24" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1382,67 +1382,67 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>69.5</v>
+        <v>74.33333333333334</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>74.5</v>
+        <v>83.91666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1.916666666666671</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>11.50000000000003</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>7.222222222222222</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>83.22222222222223</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1451,40 +1451,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>78.5</v>
+        <v>77.22222222222223</v>
       </c>
       <c r="F27" t="n">
-        <v>9.583333333333334</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G27" t="n">
-        <v>88.08333333333333</v>
+        <v>85</v>
       </c>
       <c r="H27" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I27" t="n">
-        <v>6.083333333333329</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>36.49999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>86.22222222222223</v>
+        <v>78</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>96.22222222222223</v>
+        <v>87</v>
       </c>
       <c r="H28" t="n">
         <v>104</v>
@@ -1534,23 +1534,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>84.5</v>
+        <v>89.91666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>9.5</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>94</v>
+        <v>97.83333333333334</v>
       </c>
       <c r="H29" t="n">
         <v>113</v>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.416666666666667</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="G2" t="n">
-        <v>5.416666666666667</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,12 +515,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8.5</v>
+        <v>5.238095238095238</v>
       </c>
       <c r="G3" t="n">
-        <v>8.5</v>
+        <v>5.238095238095238</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,10 +572,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.22222222222222</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>12.22222222222222</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H4" t="n">
         <v>18</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,37 +593,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5.416666666666667</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>9.583333333333334</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,115 +632,115 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>8.5</v>
+        <v>6.238095238095238</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>9.047619047619047</v>
       </c>
       <c r="G6" t="n">
-        <v>17.5</v>
+        <v>15.28571428571428</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22222222222222</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="F7" t="n">
-        <v>8.333333333333334</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G7" t="n">
-        <v>25.55555555555556</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I7" t="n">
-        <v>8.555555555555557</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>85.55555555555557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="F8" t="n">
-        <v>8.333333333333334</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G8" t="n">
-        <v>23.33333333333334</v>
+        <v>13.80952380952381</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,129 +749,129 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>17.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="H9" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.111111111111114</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>13.33333333333337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>23.33333333333334</v>
+        <v>13.80952380952381</v>
       </c>
       <c r="F10" t="n">
-        <v>8.75</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="G10" t="n">
-        <v>32.08333333333334</v>
+        <v>22.38095238095238</v>
       </c>
       <c r="H10" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>10.38095238095238</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>83.04761904761904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>25.5</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G11" t="n">
-        <v>35</v>
+        <v>28.11111111111111</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>21</v>
+        <v>73.33333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>25.55555555555556</v>
+        <v>15.28571428571428</v>
       </c>
       <c r="F12" t="n">
-        <v>7.777777777777778</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>33.33333333333334</v>
+        <v>25.28571428571428</v>
       </c>
       <c r="H12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -905,37 +905,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
         <v>5</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
-        <v>32.08333333333334</v>
+        <v>26.11111111111111</v>
       </c>
       <c r="F13" t="n">
-        <v>10.41666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>42.5</v>
+        <v>34.44444444444445</v>
       </c>
       <c r="H13" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,12 +944,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -959,55 +959,55 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>33.33333333333334</v>
+        <v>22.38095238095238</v>
       </c>
       <c r="F14" t="n">
-        <v>6.666666666666667</v>
+        <v>10.47619047619048</v>
       </c>
       <c r="G14" t="n">
-        <v>40</v>
+        <v>32.85714285714285</v>
       </c>
       <c r="H14" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>14.85714285714285</v>
       </c>
       <c r="J14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>89.14285714285712</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>25.28571428571428</v>
       </c>
       <c r="F15" t="n">
-        <v>5.5</v>
+        <v>7.619047619047619</v>
       </c>
       <c r="G15" t="n">
-        <v>44.5</v>
+        <v>32.90476190476191</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1022,28 +1022,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>28.11111111111111</v>
       </c>
       <c r="F16" t="n">
         <v>11.66666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>51.66666666666666</v>
+        <v>39.77777777777778</v>
       </c>
       <c r="H16" t="n">
         <v>53</v>
@@ -1061,31 +1061,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>43.5</v>
+        <v>32.85714285714285</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G17" t="n">
-        <v>53.5</v>
+        <v>38.57142857142857</v>
       </c>
       <c r="H17" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1100,37 +1100,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>44.5</v>
+        <v>37.90476190476191</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>51</v>
+        <v>47.90476190476191</v>
       </c>
       <c r="H18" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,37 +1139,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>34.44444444444445</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="G19" t="n">
-        <v>62</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="H19" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,37 +1178,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>56.66666666666666</v>
+        <v>38.57142857142857</v>
       </c>
       <c r="F20" t="n">
-        <v>8.333333333333334</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>44.28571428571428</v>
       </c>
       <c r="H20" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1217,37 +1217,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>53.5</v>
+        <v>39.77777777777778</v>
       </c>
       <c r="F21" t="n">
-        <v>7.083333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>60.58333333333334</v>
+        <v>51.44444444444444</v>
       </c>
       <c r="H21" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,28 +1256,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>60.58333333333334</v>
+        <v>49.28571428571428</v>
       </c>
       <c r="F22" t="n">
-        <v>8.75</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G22" t="n">
-        <v>69.33333333333334</v>
+        <v>55</v>
       </c>
       <c r="H22" t="n">
         <v>78</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,37 +1295,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>62</v>
+        <v>47.90476190476191</v>
       </c>
       <c r="F23" t="n">
+        <v>6.190476190476191</v>
+      </c>
+      <c r="G23" t="n">
+        <v>54.09523809523809</v>
+      </c>
+      <c r="H23" t="n">
+        <v>86</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>10</v>
-      </c>
-      <c r="G23" t="n">
-        <v>72</v>
-      </c>
-      <c r="H23" t="n">
-        <v>74</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,28 +1343,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>48.33333333333334</v>
       </c>
       <c r="F24" t="n">
-        <v>12.22222222222222</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>77.22222222222223</v>
+        <v>61.66666666666668</v>
       </c>
       <c r="H24" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,76 +1373,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>74.33333333333334</v>
+        <v>56.44444444444444</v>
       </c>
       <c r="F25" t="n">
-        <v>9.583333333333334</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G25" t="n">
-        <v>83.91666666666667</v>
+        <v>65.88888888888889</v>
       </c>
       <c r="H25" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I25" t="n">
-        <v>1.916666666666671</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>11.50000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>54.09523809523809</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="G26" t="n">
+        <v>64.57142857142857</v>
+      </c>
+      <c r="H26" t="n">
+        <v>81</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>9</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>72</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>78</v>
-      </c>
-      <c r="H26" t="n">
-        <v>78</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>8</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1451,12 +1451,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1466,22 +1466,22 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>77.22222222222223</v>
+        <v>55</v>
       </c>
       <c r="F27" t="n">
-        <v>7.777777777777778</v>
+        <v>7.619047619047619</v>
       </c>
       <c r="G27" t="n">
-        <v>85</v>
+        <v>62.61904761904762</v>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1490,37 +1490,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>78</v>
+        <v>61.66666666666668</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G28" t="n">
-        <v>87</v>
+        <v>72.77777777777779</v>
       </c>
       <c r="H28" t="n">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,40 +1529,703 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>ORD34</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>62.61904761904762</v>
+      </c>
+      <c r="F29" t="n">
+        <v>10.47619047619048</v>
+      </c>
+      <c r="G29" t="n">
+        <v>73.0952380952381</v>
+      </c>
+      <c r="H29" t="n">
+        <v>80</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ORD18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>67.57142857142857</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
+        <v>77.57142857142857</v>
+      </c>
+      <c r="H30" t="n">
+        <v>78</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ORD42</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>65.88888888888889</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12.22222222222222</v>
+      </c>
+      <c r="G31" t="n">
+        <v>78.11111111111111</v>
+      </c>
+      <c r="H31" t="n">
+        <v>81</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ORD28</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>72.77777777777779</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.77777777777778</v>
+      </c>
+      <c r="G32" t="n">
+        <v>85.55555555555557</v>
+      </c>
+      <c r="H32" t="n">
+        <v>82</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.555555555555571</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>21.33333333333343</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ORD36</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>73.0952380952381</v>
+      </c>
+      <c r="F33" t="n">
+        <v>10.95238095238095</v>
+      </c>
+      <c r="G33" t="n">
+        <v>84.04761904761905</v>
+      </c>
+      <c r="H33" t="n">
+        <v>82</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.047619047619051</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>12.28571428571431</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ORD44</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>77.57142857142857</v>
+      </c>
+      <c r="F34" t="n">
+        <v>10.95238095238095</v>
+      </c>
+      <c r="G34" t="n">
+        <v>88.52380952380952</v>
+      </c>
+      <c r="H34" t="n">
+        <v>82</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6.523809523809518</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>39.14285714285711</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ORD17</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>78.11111111111111</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.777777777777778</v>
+      </c>
+      <c r="G35" t="n">
+        <v>85.88888888888889</v>
+      </c>
+      <c r="H35" t="n">
+        <v>85</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8888888888888857</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" t="n">
+        <v>11.55555555555551</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ORD45</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>89.04761904761905</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="G36" t="n">
+        <v>94.28571428571429</v>
+      </c>
+      <c r="H36" t="n">
+        <v>110</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ORD23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>85.55555555555557</v>
+      </c>
+      <c r="F37" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" t="n">
+        <v>95.55555555555557</v>
+      </c>
+      <c r="H37" t="n">
+        <v>99</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ORD39</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>85.88888888888889</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" t="n">
+        <v>95.88888888888889</v>
+      </c>
+      <c r="H38" t="n">
+        <v>99</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ORD31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>88.52380952380952</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="G39" t="n">
+        <v>97.09523809523809</v>
+      </c>
+      <c r="H39" t="n">
+        <v>99</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ORD40</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>94.28571428571429</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="G40" t="n">
+        <v>103.3333333333333</v>
+      </c>
+      <c r="H40" t="n">
+        <v>106</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>12</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ORD32</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>95.55555555555557</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10.55555555555556</v>
+      </c>
+      <c r="G41" t="n">
+        <v>106.1111111111111</v>
+      </c>
+      <c r="H41" t="n">
+        <v>106</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1111111111111285</v>
+      </c>
+      <c r="J41" t="n">
+        <v>12</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.333333333333542</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ORD30</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>97.88888888888889</v>
+      </c>
+      <c r="F42" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="G42" t="n">
+        <v>111.2222222222222</v>
+      </c>
+      <c r="H42" t="n">
+        <v>115</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>13</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>ORD24</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C43" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>97.09523809523809</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="G43" t="n">
+        <v>106.1428571428571</v>
+      </c>
+      <c r="H43" t="n">
+        <v>106</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1428571428571388</v>
+      </c>
+      <c r="J43" t="n">
+        <v>13</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.857142857142804</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ORD38</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>13</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>103.3333333333333</v>
+      </c>
+      <c r="F44" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="G44" t="n">
+        <v>114.7619047619048</v>
+      </c>
+      <c r="H44" t="n">
+        <v>115</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>13</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ORD29</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
         <v>10</v>
       </c>
-      <c r="D29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>89.91666666666667</v>
-      </c>
-      <c r="F29" t="n">
-        <v>7.916666666666667</v>
-      </c>
-      <c r="G29" t="n">
-        <v>97.83333333333334</v>
-      </c>
-      <c r="H29" t="n">
-        <v>113</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>106.1111111111111</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="G45" t="n">
+        <v>112.2222222222222</v>
+      </c>
+      <c r="H45" t="n">
+        <v>110</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.222222222222243</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>20.00000000000018</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ORD37</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
         <v>12</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>106.1428571428571</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5.238095238095238</v>
+      </c>
+      <c r="G46" t="n">
+        <v>111.3809523809524</v>
+      </c>
+      <c r="H46" t="n">
+        <v>110</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.38095238095238</v>
+      </c>
+      <c r="J46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>12.42857142857142</v>
       </c>
     </row>
   </sheetData>

--- a/Results_SA_improved.xlsx
+++ b/Results_SA_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -500,13 +500,13 @@
         <v>8.095238095238095</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5.238095238095238</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="G3" t="n">
-        <v>5.238095238095238</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.333333333333334</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G4" t="n">
-        <v>8.333333333333334</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -611,19 +611,19 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7.777777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G5" t="n">
-        <v>7.777777777777778</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,22 +647,22 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6.238095238095238</v>
+        <v>7.111111111111111</v>
       </c>
       <c r="F6" t="n">
-        <v>9.047619047619047</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G6" t="n">
-        <v>15.28571428571428</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -686,13 +686,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>7.777777777777778</v>
+        <v>8.095238095238095</v>
       </c>
       <c r="F7" t="n">
-        <v>7.222222222222222</v>
+        <v>6.190476190476191</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="H7" t="n">
         <v>28</v>
@@ -710,12 +710,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD35</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -725,36 +725,36 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8.095238095238095</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="F8" t="n">
-        <v>5.714285714285714</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>13.80952380952381</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="H8" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>7.444444444444443</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>59.55555555555554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.333333333333334</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="F9" t="n">
-        <v>12.77777777777778</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="G9" t="n">
-        <v>21.11111111111111</v>
+        <v>18.09523809523809</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I9" t="n">
-        <v>1.111111111111114</v>
+        <v>0.0952380952380949</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>13.33333333333337</v>
+        <v>0.952380952380949</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -803,70 +803,70 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13.80952380952381</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F10" t="n">
-        <v>8.571428571428571</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>22.38095238095238</v>
+        <v>20.95238095238095</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="I10" t="n">
-        <v>10.38095238095238</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>83.04761904761904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>11.11111111111111</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G11" t="n">
-        <v>28.11111111111111</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I11" t="n">
-        <v>6.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>73.33333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -878,73 +878,73 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>15.28571428571428</v>
+        <v>23.09523809523809</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="G12" t="n">
-        <v>25.28571428571428</v>
+        <v>32.61904761904762</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>10.61904761904762</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>127.4285714285714</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>26.11111111111111</v>
+        <v>19.44444444444444</v>
       </c>
       <c r="F13" t="n">
-        <v>8.333333333333334</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G13" t="n">
-        <v>34.44444444444445</v>
+        <v>31.66666666666666</v>
       </c>
       <c r="H13" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>13.66666666666666</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>81.99999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -956,39 +956,39 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>22.38095238095238</v>
+        <v>21.95238095238095</v>
       </c>
       <c r="F14" t="n">
-        <v>10.47619047619048</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>32.85714285714285</v>
+        <v>31.95238095238095</v>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="I14" t="n">
-        <v>14.85714285714285</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>89.14285714285712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -998,31 +998,31 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>25.28571428571428</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="F15" t="n">
-        <v>7.619047619047619</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>32.90476190476191</v>
+        <v>38.22222222222222</v>
       </c>
       <c r="H15" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.2222222222222214</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2.888888888888879</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD41</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1037,22 +1037,22 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>28.11111111111111</v>
+        <v>31.66666666666666</v>
       </c>
       <c r="F16" t="n">
-        <v>11.66666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>39.77777777777778</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1073,25 +1073,25 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>32.85714285714285</v>
+        <v>36.95238095238095</v>
       </c>
       <c r="F17" t="n">
-        <v>5.714285714285714</v>
+        <v>11.90476190476191</v>
       </c>
       <c r="G17" t="n">
-        <v>38.57142857142857</v>
+        <v>48.85714285714285</v>
       </c>
       <c r="H17" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1109,19 +1109,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>37.90476190476191</v>
+        <v>32.61904761904762</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>47.90476190476191</v>
+        <v>42.61904761904762</v>
       </c>
       <c r="H18" t="n">
         <v>53</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1148,28 +1148,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>34.44444444444445</v>
+        <v>38.22222222222222</v>
       </c>
       <c r="F19" t="n">
-        <v>13.88888888888889</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G19" t="n">
-        <v>48.33333333333334</v>
+        <v>47.11111111111111</v>
       </c>
       <c r="H19" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1178,28 +1178,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD43</t>
+          <t>ORD35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>38.57142857142857</v>
+        <v>38.33333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>5.714285714285714</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>44.28571428571428</v>
+        <v>44.99999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>78</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1232,13 +1232,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>39.77777777777778</v>
+        <v>42.61904761904762</v>
       </c>
       <c r="F21" t="n">
-        <v>11.66666666666667</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>51.44444444444444</v>
+        <v>52.61904761904762</v>
       </c>
       <c r="H21" t="n">
         <v>53</v>
@@ -1256,28 +1256,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>49.28571428571428</v>
+        <v>44.99999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>5.714285714285714</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>55</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="H22" t="n">
         <v>78</v>
@@ -1295,12 +1295,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1310,22 +1310,22 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>47.90476190476191</v>
+        <v>47.11111111111111</v>
       </c>
       <c r="F23" t="n">
-        <v>6.190476190476191</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>54.09523809523809</v>
+        <v>53.77777777777778</v>
       </c>
       <c r="H23" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>48.33333333333334</v>
+        <v>48.85714285714285</v>
       </c>
       <c r="F24" t="n">
-        <v>13.33333333333333</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="G24" t="n">
-        <v>61.66666666666668</v>
+        <v>60.28571428571428</v>
       </c>
       <c r="H24" t="n">
         <v>66</v>
@@ -1373,7 +1373,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1382,28 +1382,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>56.44444444444444</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="F25" t="n">
-        <v>9.444444444444445</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G25" t="n">
         <v>65.88888888888889</v>
       </c>
       <c r="H25" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,28 +1421,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>54.09523809523809</v>
+        <v>52.61904761904762</v>
       </c>
       <c r="F26" t="n">
-        <v>10.47619047619048</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="G26" t="n">
-        <v>64.57142857142857</v>
+        <v>59.76190476190477</v>
       </c>
       <c r="H26" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1451,37 +1451,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>55</v>
+        <v>53.77777777777778</v>
       </c>
       <c r="F27" t="n">
-        <v>7.619047619047619</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G27" t="n">
-        <v>62.61904761904762</v>
+        <v>66</v>
       </c>
       <c r="H27" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1495,23 +1495,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>61.66666666666668</v>
+        <v>59.76190476190477</v>
       </c>
       <c r="F28" t="n">
-        <v>11.11111111111111</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="G28" t="n">
-        <v>72.77777777777779</v>
+        <v>69.28571428571429</v>
       </c>
       <c r="H28" t="n">
         <v>76</v>
@@ -1529,7 +1529,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD34</t>
+          <t>ORD42</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1538,22 +1538,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>62.61904761904762</v>
+        <v>65.28571428571428</v>
       </c>
       <c r="F29" t="n">
         <v>10.47619047619048</v>
       </c>
       <c r="G29" t="n">
-        <v>73.0952380952381</v>
+        <v>75.76190476190476</v>
       </c>
       <c r="H29" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1568,37 +1568,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>67.57142857142857</v>
+        <v>65.88888888888889</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G30" t="n">
-        <v>77.57142857142857</v>
+        <v>78.11111111111111</v>
       </c>
       <c r="H30" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1607,37 +1607,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORD42</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>65.88888888888889</v>
+        <v>66</v>
       </c>
       <c r="F31" t="n">
-        <v>12.22222222222222</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>78.11111111111111</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="H31" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1651,41 +1651,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>72.77777777777779</v>
+        <v>69.28571428571429</v>
       </c>
       <c r="F32" t="n">
-        <v>12.77777777777778</v>
+        <v>10.95238095238095</v>
       </c>
       <c r="G32" t="n">
-        <v>85.55555555555557</v>
+        <v>80.23809523809524</v>
       </c>
       <c r="H32" t="n">
         <v>82</v>
       </c>
       <c r="I32" t="n">
-        <v>3.555555555555571</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>21.33333333333343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORD36</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1694,31 +1694,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>73.0952380952381</v>
+        <v>75.76190476190476</v>
       </c>
       <c r="F33" t="n">
-        <v>10.95238095238095</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G33" t="n">
-        <v>84.04761904761905</v>
+        <v>82.42857142857143</v>
       </c>
       <c r="H33" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I33" t="n">
-        <v>2.047619047619051</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>12.28571428571431</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1739,31 +1739,31 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>77.57142857142857</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="F34" t="n">
-        <v>10.95238095238095</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G34" t="n">
-        <v>88.52380952380952</v>
+        <v>90.44444444444446</v>
       </c>
       <c r="H34" t="n">
         <v>82</v>
       </c>
       <c r="I34" t="n">
-        <v>6.523809523809518</v>
+        <v>8.444444444444457</v>
       </c>
       <c r="J34" t="n">
         <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>39.14285714285711</v>
+        <v>50.66666666666674</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1772,67 +1772,67 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>78.11111111111111</v>
+        <v>81.11111111111111</v>
       </c>
       <c r="F35" t="n">
-        <v>7.777777777777778</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="G35" t="n">
-        <v>85.88888888888889</v>
+        <v>93.88888888888889</v>
       </c>
       <c r="H35" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8888888888888857</v>
+        <v>11.88888888888889</v>
       </c>
       <c r="J35" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>11.55555555555551</v>
+        <v>71.33333333333331</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORD45</t>
+          <t>ORD32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>89.04761904761905</v>
+        <v>80.23809523809524</v>
       </c>
       <c r="F36" t="n">
-        <v>5.238095238095238</v>
+        <v>9.047619047619047</v>
       </c>
       <c r="G36" t="n">
-        <v>94.28571428571429</v>
+        <v>89.28571428571429</v>
       </c>
       <c r="H36" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1841,28 +1841,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>85.55555555555557</v>
+        <v>82.42857142857143</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="G37" t="n">
-        <v>95.55555555555557</v>
+        <v>91</v>
       </c>
       <c r="H37" t="n">
         <v>99</v>
@@ -1880,28 +1880,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ORD39</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>85.88888888888889</v>
+        <v>89.28571428571429</v>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="G38" t="n">
-        <v>95.88888888888889</v>
+        <v>97.85714285714286</v>
       </c>
       <c r="H38" t="n">
         <v>99</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1934,25 +1934,25 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>88.52380952380952</v>
+        <v>90.44444444444446</v>
       </c>
       <c r="F39" t="n">
-        <v>8.571428571428571</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>97.09523809523809</v>
+        <v>100.4444444444445</v>
       </c>
       <c r="H39" t="n">
         <v>99</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1.444444444444457</v>
       </c>
       <c r="J39" t="n">
         <v>9</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>13.00000000000011</v>
       </c>
     </row>
     <row r="40">
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>94.28571428571429</v>
+        <v>92</v>
       </c>
       <c r="F40" t="n">
         <v>9.047619047619047</v>
       </c>
       <c r="G40" t="n">
-        <v>103.3333333333333</v>
+        <v>101.0476190476191</v>
       </c>
       <c r="H40" t="n">
         <v>106</v>
@@ -1997,76 +1997,76 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ORD32</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>95.55555555555557</v>
+        <v>93.88888888888889</v>
       </c>
       <c r="F41" t="n">
         <v>10.55555555555556</v>
       </c>
       <c r="G41" t="n">
-        <v>106.1111111111111</v>
+        <v>104.4444444444444</v>
       </c>
       <c r="H41" t="n">
         <v>106</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1111111111111285</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>1.333333333333542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ORD30</t>
+          <t>ORD29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>97.88888888888889</v>
+        <v>97.85714285714286</v>
       </c>
       <c r="F42" t="n">
-        <v>13.33333333333333</v>
+        <v>5.238095238095238</v>
       </c>
       <c r="G42" t="n">
-        <v>111.2222222222222</v>
+        <v>103.0952380952381</v>
       </c>
       <c r="H42" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2075,40 +2075,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>97.09523809523809</v>
+        <v>105.4444444444445</v>
       </c>
       <c r="F43" t="n">
-        <v>9.047619047619047</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G43" t="n">
-        <v>106.1428571428571</v>
+        <v>111.5555555555556</v>
       </c>
       <c r="H43" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1428571428571388</v>
+        <v>1.555555555555571</v>
       </c>
       <c r="J43" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>1.857142857142804</v>
+        <v>15.55555555555571</v>
       </c>
     </row>
     <row r="44">
@@ -2123,19 +2123,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>103.3333333333333</v>
+        <v>101.0476190476191</v>
       </c>
       <c r="F44" t="n">
         <v>11.42857142857143</v>
       </c>
       <c r="G44" t="n">
-        <v>114.7619047619048</v>
+        <v>112.4761904761905</v>
       </c>
       <c r="H44" t="n">
         <v>115</v>
@@ -2153,40 +2153,40 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ORD29</t>
+          <t>ORD30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>106.1111111111111</v>
+        <v>103.0952380952381</v>
       </c>
       <c r="F45" t="n">
-        <v>6.111111111111111</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="G45" t="n">
-        <v>112.2222222222222</v>
+        <v>114.5238095238095</v>
       </c>
       <c r="H45" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I45" t="n">
-        <v>2.222222222222243</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K45" t="n">
-        <v>20.00000000000018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2197,35 +2197,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>106.1428571428571</v>
+        <v>104.4444444444444</v>
       </c>
       <c r="F46" t="n">
-        <v>5.238095238095238</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G46" t="n">
-        <v>111.3809523809524</v>
+        <v>110.5555555555556</v>
       </c>
       <c r="H46" t="n">
         <v>110</v>
       </c>
       <c r="I46" t="n">
-        <v>1.38095238095238</v>
+        <v>0.5555555555555571</v>
       </c>
       <c r="J46" t="n">
         <v>9</v>
       </c>
       <c r="K46" t="n">
-        <v>12.42857142857142</v>
+        <v>5.000000000000014</v>
       </c>
     </row>
   </sheetData>
